--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_07_Structural_Properties_of_Matter.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_07_Structural_Properties_of_Matter.xlsx
@@ -1054,11 +1054,6 @@
           <t>একটি সমসত্ত্ব ও আইসোট্রপিক উপাদানের ইয়ং-এর গুণাঙ্ক $Y$, আয়তন গুণাঙ্ক $K$, ব্যবর্তন গুণাঙ্ক $\eta$ এবং পয়সনের অনুপাত $\sigma$। এদের মধ্যকার দুটি মৌলিক সমীকরণ $Y = 3K(1 - 2\sigma)$ এবং $Y = 2\eta(1 + \sigma)$ ব্যবহার করে প্রমাণ কর যে পয়সনের অনুপাতের তাত্ত্বিক সীমা $-1 \le \sigma \le 0.5$।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>সমীকরণদ্বয়: (১) $1 - 2\sigma = \frac{Y}{3K}$ এবং (২) $1 + \sigma = \frac{Y}{2\eta}$। কোনো স্থিতিশীল উপাদানে বিকৃতির বিরুদ্ধে অভ্যন্তরীণ প্রত্যয়নী বল কাজ করে, ফলে স্থিতিস্থাপক গুণাঙ্কসমূহ সর্বদা ধনাত্মক হতে হবে ($Y &gt; 0, K &gt; 0, \eta &gt; 0$)। সমীকরণ (১) থেকে: $K &gt; 0 \implies 1 - 2\sigma &gt; 0 \implies 2\sigma &lt; 1 \implies \sigma &lt; 0.5$। সমীকরণ (২) থেকে: $\eta &gt; 0 \implies 1 + \sigma &gt; 0 \implies \sigma &gt; -1$। উভয় অসমতা একত্রিত করলে পাওয়া যায়: $-1 \le \sigma \le 0.5$। বাস্তবে অধিকাংশ ধাতব পদার্থের জন্য $\sigma$-এর মান $0.25$ থেকে $0.35$-এর মধ্যে থাকে। যদি কোনো উপাদান সম্পূর্ণ অসংকোচনীয় হয় (যেমন রাবার বা জল), তবে আয়তন পরিবর্তন শূন্য হয় ($\Delta V = 0 \implies K \to \infty$), যার ফলে $\sigma = 0.5$ হয়।</t>
@@ -1104,11 +1099,6 @@
           <t>একটি কঠিন ঘনকের তিনটি অক্ষ বরাবর যথাক্রমে $\sigma_x, \sigma_y, \sigma_z$ অনুদৈর্ঘ্য পীড়ন প্রয়োগ করা হলো। উপাদানটির ইয়ং-এর গুণাঙ্ক $Y$ এবং পয়সনের অনুপাত $\sigma$ হলে ঘনকটির একক আয়তনের পরিবর্তন (আয়তন বিকৃতি $\frac{\Delta V}{V}$) নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>হুকের সূত্রের সাধারণ ত্রিমাত্রিক রূপ অনুসারে $x$-অক্ষ বরাবর অনুদৈর্ঘ্য বিকৃতি হলো নিজস্ব পীড়নের প্রসারণ এবং অপর দুই অক্ষের পীড়নজনিত পার্শ্ব বিকৃতির সমষ্টি: $\epsilon_x = \frac{\sigma_x}{Y} - \frac{\sigma}{Y}(\sigma_y + \sigma_z)$। একইভাবে $y$ ও $z$ অক্ষের বিকৃতি: $\epsilon_y = \frac{\sigma_y}{Y} - \frac{\sigma}{Y}(\sigma_z + \sigma_x)$ এবং $\epsilon_z = \frac{\sigma_z}{Y} - \frac{\sigma}{Y}(\sigma_x + \sigma_y)$। ক্ষুদ্র বিকৃতির ক্ষেত্রে মোট আয়তন বিকৃতি তিনটি রৈখিক বিকৃতির যোগফলের সমান: $\frac{\Delta V}{V} \approx \epsilon_x + \epsilon_y + \epsilon_z = \frac{\sigma_x + \sigma_y + \sigma_z}{Y} - \frac{2\sigma}{Y}(\sigma_x + \sigma_y + \sigma_z) = \frac{1 - 2\sigma}{Y}(\sigma_x + \sigma_y + \sigma_z)$। হাইড্রোস্ট্যাটিক চাপের ক্ষেত্রে ($\sigma_x = \sigma_y = \sigma_z = -P$) এটি $\frac{\Delta V}{V} = -\frac{3(1-2\sigma)}{Y}P = -\frac{P}{K}$ প্রদান করে।</t>
@@ -1154,11 +1144,6 @@
           <t>$L$ দৈর্ঘ্য ও $R$ ব্যাসার্ধের একটি নিরেট তারের এক প্রান্ত দৃঢ়ভাবে আটকিয়ে অপর প্রান্তে অক্ষের সাপেক্ষে $\theta$ কোণে মোচড় (Twist) দেওয়া হলো। তারের বহিঃপৃষ্ঠে এবং কেন্দ্র থেকে $r$ ব্যাসার্ধে ব্যবর্তন বিকৃতি (Shear Strain $\phi$) কত?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>তারের কেন্দ্র থেকে $r$ দূরত্বের একটি সিলিন্ডারীয় খোলস বিবেচনা করি। এক প্রান্তে অক্ষ সাপেক্ষে মোচড় কোণ $\theta$ হলে পরিধি বরাবর আর্ক সরণ $s = r\theta$। এই সরণটি তারের দৈর্ঘ্য $L$ বরাবর রৈখিকভাবে প্রসারিত হয়। ব্যবর্তন বিকৃতির সংজ্ঞা হলো কোণীয় বিচ্যুতি: $\phi(r) = \frac{s}{L} = \frac{r\theta}{L}$। অতএব কেন্দ্র থেকে দূরত্বের সমানুপাতিক হারে ব্যবর্তন বিকৃতি বৃদ্ধি পায়। তারের কেন্দ্রে ($r=0$) বিকৃতি শূন্য এবং বহিঃপৃষ্ঠে ($r=R$) বিকৃতি সর্বোচ্চ: $\phi_{\max} = \frac{R\theta}{L}$।</t>
@@ -1204,11 +1189,6 @@
           <t>একই উপাদান, একই দৈর্ঘ্য এবং একই ভরের একটি নিরেট তার (ব্যাসার্ধ $R$) এবং একটি ফাঁপা সিলিন্ডার (বহিঃব্যাসার্ধ $R_2$, অন্তঃব্যাসার্ধ $R_1$) তৈরি করা হলো। এদের প্রতি একক মোচড় কোণের জন্য প্রয়োজনীয় টর্কের অনুপাত নির্ণয় কর এবং ফাঁপা পাইপ কেন অধিকতর দৃঢ়?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>একটি সিলিন্ডারের টরশনাল কাপল $C = \frac{\pi \eta R^4}{2L}$। ফাঁপা সিলিন্ডারের জন্য $C_h = \frac{\pi \eta (R_2^4 - R_1^4)}{2L}$। সমান ভরের শর্ত: $\pi R^2 L \rho = \pi (R_2^2 - R_1^2) L \rho \implies R^2 = R_2^2 - R_1^2$। টর্শনাল কাপলের অনুপাত: $\frac{C_h}{C} = \frac{R_2^4 - R_1^4}{R^4} = \frac{(R_2^2 - R_1^2)(R_2^2 + R_1^2)}{(R^2)^2} = \frac{R^2 (R_2^2 + R_1^2)}{R^4} = \frac{R_2^2 + R_1^2}{R^2} = \frac{R_2^2 + R_1^2}{R_2^2 - R_1^2} &gt; 1$। যেহেতু $R_2 &gt; R$, সেহেতু $\frac{C_h}{C} &gt; 1$ সর্বদা। ফাঁপা সিলিন্ডারে উপাদানটি অক্ষ থেকে অধিক দূরে অবস্থান করায় জড়তার পোলার মোমেন্ট বেশি হয়, যার ফলে একই ভরের ফাঁপা পাইপ মোচড়ের বিরুদ্ধে অনেক বেশি শক্তিশালী ও টেকসই হয়।</t>
@@ -1254,11 +1234,6 @@
           <t>একটি ধাতব তারের দৈর্ঘ্য $0.2\%$ বৃদ্ধি করা হলো। তারের উপাদানের পয়সনের অনুপাত $\sigma = 0.3$ হলে তারটির ব্যাস এবং আয়তনের শতকরা পরিবর্তন কত?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>অনুদৈর্ঘ্য বিকৃতি $\frac{\Delta L}{L} = +0.2\% = +0.002$। পয়সনের অনুপাতের সংজ্ঞা $\sigma = -\frac{\Delta D/D}{\Delta L/L} \implies \frac{\Delta D}{D} = -\sigma \frac{\Delta L}{L} = -0.3 \times (+0.2\%) = -0.06\%$। তারটির ব্যাস $0.06\%$ হ্রাস পায়। তারের আয়তন $V = \frac{\pi}{4}D^2 L$। ক্ষুদ্র পরিবর্তনে ব্যবকলন করি: $\frac{\Delta V}{V} \approx \frac{\Delta L}{L} + 2\frac{\Delta D}{D} = \frac{\Delta L}{L}(1 - 2\sigma) = (+0.2\%)(1 - 2(0.3)) = (+0.2\%)(0.4) = +0.08\%$। অর্থাৎ দৈর্ঘ্য বৃদ্ধি পেলেও পার্শ্ব সংঙ্কোচনের কারণে নিট আয়তন মাত্র $0.08\%$ বৃদ্ধি পায়।</t>
@@ -1304,11 +1279,6 @@
           <t>$L$ দৈর্ঘ্য, $b$ প্রস্থ এবং $d$ গভীরতার একটি সুষম আয়তাকার বিম দুই প্রান্তে দুটি ছুরিকাধারের (Knife edges) ওপর স্থাপিত। বিমের ঠিক মধ্যবিন্দুতে $W = Mg$ ভার চাপালে কেন্দ্রবিন্দুর উল্লম্ব অবনমন $\delta$ নির্ণয়ের সূত্র প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>বিম নমনকালে উপরের অংশ সংকুচিত ও নিচের অংশ প্রসারিত হয় এবং মধ্যবর্তী নিরপেক্ষ স্তর (Neutral Surface) অপরিবর্তিত থাকে। জ্যামিতিক জড়তার ভ্রামক $I_g = \frac{b d^3}{12}$। নমন টর্কের সমীকরণ $\frac{Y I_g}{R} = M_b(x) = \frac{W}{2}x$। ব্যবকলনীয় সমীকরণ $Y I_g \frac{d^2 y}{dx^2} = \frac{W}{2}x$ দুইবার সমাকলন করে বাউন্ডারি শর্ত ($x=0$-তে $y=0$ এবং $x=L/2$-তে $\frac{dy}{dx}=0$) প্রয়োগ করলে কেন্দ্রের সর্বোচ্চ অবনমন পাওয়া যায়: $\delta = \frac{W L^3}{48 Y I_g} = \frac{W L^3}{48 Y (b d^3 / 12)} = \frac{W L^3}{4 Y b d^3}$। লক্ষণীয় যে বিমের গভীরতা $d$-এর ওপর নির্ভরতা ঘনকীয় ($d^3$), তাই বিমকে চ্যাপ্টা না রেখে খাড়াভাবে (যেমন 'I' আকৃতির গার্ডার) বসালে নমন অত্যন্ত কার্যকরভাবে হ্রাস পায়।</t>
@@ -1354,11 +1324,6 @@
           <t>$L$ দৈর্ঘ্য এবং আয়তাকার প্রস্থচ্ছেদের ($b \times d$) একটি হালকা বিমের এক প্রান্ত দেয়ালে অনুভূমিকভাবে দৃঢ়ভাবে আটকানো (ক্যান্টিলিভার)। মুক্ত প্রান্তে $W$ ভার ঝুলালে মুক্ত প্রান্তের উল্লম্ব অবনমন $\delta_{\text{cant}}$ কত?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>দেয়াল থেকে $x$ দূরত্বে ক্যান্টিলিভারের নমন টর্ক $M_b(x) = W(L - x)$। ব্যবকলনীয় সমীকরণ: $Y I_g \frac{d^2 y}{dx^2} = W(L - x)$। প্রথম সমাকলন: $Y I_g \frac{dy}{dx} = W\left(Lx - \frac{x^2}{2}\right)$ (যেহেতু $x=0$-তে ঢাল $0$)। দ্বিতীয় সমাকলন: $Y I_g y = W\left(\frac{L x^2}{2} - \frac{x^3}{6}\right)$। মুক্ত প্রান্তে $x = L$ বসালে: $\delta_{\text{cant}} = y(L) = \frac{W}{Y I_g}\left(\frac{L^3}{2} - \frac{L^3}{6}\right) = \frac{W L^3}{3 Y I_g}$। আয়তাকার বিমের $I_g = \frac{b d^3}{12}$ বসিয়ে পাই: $\delta_{\text{cant}} = \frac{W L^3}{3 Y (b d^3 / 12)} = \frac{4 W L^3}{Y b d^3}$।</t>
@@ -1455,11 +1420,6 @@
           <t>সমান দৈর্ঘ্য $L$ কিন্তু ভিন্ন উপাদান ($Y_1, A_1$) ও ($Y_2, A_2$)-এর দুটি তার দুই প্রান্তে দৃঢ়ভাবে একসাথে বাঁধা। এই যৌথ সংস্থায় মোট টান $F$ প্রয়োগ করলে সংস্থার তুল্য ইয়ং-এর গুণাঙ্ক $Y_{\text{eq}}$ কত?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>উভয় তার একসাথে বাঁধা থাকায় তাদের প্রসারণ সমান: $\Delta L_1 = \Delta L_2 = \Delta L$। ফলে উভয় তারের অনুদৈর্ঘ্য বিকৃতি সমান: $\epsilon = \frac{\Delta L}{L}$। প্রযুক্ত মোট বল তারদ্বয়ের টানের সমষ্টি: $F = F_1 + F_2 = Y_1 A_1 \left(\frac{\Delta L}{L}\right) + Y_2 A_2 \left(\frac{\Delta L}{L}\right) = (Y_1 A_1 + Y_2 A_2)\frac{\Delta L}{L}$। যৌথ তারের মোট প্রস্থচ্ছেদ $A = A_1 + A_2$। তুল্য ইয়ং-এর গুণাঙ্ক সংজ্ঞায়িত হয় $F = Y_{\text{eq}}(A_1 + A_2)\frac{\Delta L}{L}$ হিসেবে। দুটি তুলনা করে পাই: $Y_{\text{eq}}(A_1 + A_2) = Y_1 A_1 + Y_2 A_2 \implies Y_{\text{eq}} = \frac{Y_1 A_1 + Y_2 A_2}{A_1 + A_2}$।</t>
@@ -1505,11 +1465,6 @@
           <t>$R$ ব্যাসার্ধ এবং $\rho$ ঘনত্বের একটি সরু বৃত্তাকার রিং তার কেন্দ্রগামী ও তলের লম্ব অক্ষের সাপেক্ষে $\omega$ কৌণিক বেগে অনুভূমিক তলে ঘুরছে। রিংয়ের ভেতরে উৎপন্ন অনুদৈর্ঘ্য টান পীড়ন (Tensile Stress $\sigma$) নির্ণয় কর এবং ব্রেকিং স্ট্রেস $\sigma_b$ হলে সর্বোচ্চ নিরাপদ কৌণিক বেগ কত?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>রিংয়ের একটি ক্ষুদ্রাংশ $d\theta$ বিবেচনা করি যার ভর $dm = \rho A R d\theta$। এই অংশের প্রয়োজনীয় কেন্দ্রমুখী বল $dF_c = dm \omega^2 R = \rho A R^2 \omega^2 d\theta$। রিংয়ের উভয় প্রান্তের টান $T$ এই বল যোগায়: $2T\sin\left(\frac{d\theta}{2}\right) \approx T d\theta$। কেন্দ্রমুখী বলের সাথে সমতা করে পাই: $T d\theta = \rho A R^2 \omega^2 d\theta \implies T = \rho A R^2 \omega^2$। অতএব রিংয়ের উপাদানটিতে সৃষ্ট প্রসার্য পীড়ন $\sigma = \frac{T}{A} = \rho R^2 \omega^2 = \rho v^2$, যা রিংয়ের প্রস্থচ্ছেদের ক্ষেত্রফলের ওপর নির্ভর করে না। সর্বোচ্চ নিরাপদ কৌণিক বেগ $\omega_{\max} = \frac{1}{R}\sqrt{\frac{\sigma_b}{\rho}}$।</t>
@@ -1555,11 +1510,6 @@
           <t>প্রমাণ কর যে একটি প্রসারিত স্থিতিস্থাপক তারের প্রতি একক আয়তনে সঞ্চিত বিভব শক্তি (Energy Density) $u = \frac{1}{2} \times \text{পীড়ন} \times \text{বিকৃতি} = \frac{\sigma^2}{2Y} = \frac{1}{2}Y\epsilon^2$।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>$L$ দৈর্ঘ্য ও $A$ প্রস্থচ্ছেদের একটি তারকে $x$ পরিমাণ প্রসারিত করতে প্রয়োজনীয় বল $F(x) = \frac{YA}{L}x$। অতিরিক্ত ক্ষুদ্র প্রসারণ $dx$-এ কৃতকাজ $dW = F(x)dx = \frac{YA}{L}x dx$। শূন্য থেকে $\Delta L$ প্রসারণে মোট কৃতকাজ: $W = \int_0^{\Delta L} \frac{YA}{L}x dx = \frac{YA}{2L}(\Delta L)^2 = \frac{1}{2}\left(\frac{YA\Delta L}{L}\right)\Delta L = \frac{1}{2}F \Delta L$। এই কাজ তারের ভেতর বিভব শক্তি হিসেবে জমা থাকে: $U = \frac{1}{2}F \Delta L$। তারের আয়তন $V = A L$। অতএব প্রতি একক আয়তনে সঞ্চিত শক্তি $u = \frac{U}{V} = \frac{\frac{1}{2}F \Delta L}{AL} = \frac{1}{2}\left(\frac{F}{A}\right)\left(\frac{\Delta L}{L}\right) = \frac{1}{2} \times \text{পীড়ন} \times \text{বিকৃতি}$। পীড়ন = $Y \times$ বিকৃতি বসিয়ে পাই $u = \frac{1}{2}Y\epsilon^2 = \frac{\sigma^2}{2Y}$।</t>
@@ -1605,11 +1555,6 @@
           <t>$L$ দৈর্ঘ্য, $A$ প্রস্থচ্ছেদ এবং মোট ভর $M$ বিশিষ্ট একটি সুষম ভারী উল্লম্ব তার ছাদ থেকে মুক্তভাবে ঝুলছে। তারটির নিজস্ব ওজনের কারণে এর মোট প্রসারণ $\Delta L$ নির্ণয় কর এবং দেখাও যে এটি মুক্ত প্রান্তে $M/2$ ভর ঝুলালে প্রসারণের সমান।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>তারের মুক্ত নিচের প্রান্ত থেকে $y$ উচ্চতায় একটি ক্ষুদ্রাংশ $dy$ বিবেচনা করি। এই অংশের নিচে থাকা তারের দৈর্ঘ্য $y$ এবং ভর $m(y) = \frac{M}{L}y$। ওই অংশে টান $T(y) = m(y)g = \frac{Mgy}{L}$। $dy$ অংশের প্রসারণ $d(\Delta L) = \frac{T(y)dy}{YA} = \frac{Mgy}{YAL}dy$। সম্পূর্ণ তারের জন্য সমাকলন করি ($0 \le y \le L$): $\Delta L = \int_0^L \frac{Mgy}{YAL}dy = \frac{Mg}{YAL}\left[\frac{y^2}{2}\right]_0^L = \frac{MgL}{2YA}$। যদি তারটির নিজস্ব ওজন নগণ্য হতো এবং মুক্ত প্রান্তে $M/2$ ভর ঝুলানো হতো, তবে সম্পূর্ণ তারে টান থাকত ধ্রুব $T = \frac{Mg}{2}$, যার ফলে প্রসারণ হতো $\frac{(Mg/2)L}{YA} = \frac{MgL}{2YA}$। অতএব নিজস্ব ওজনে প্রসারণ মুক্ত প্রান্তে অর্ধেক ভর ঝুলালে প্রসারণের সমান।</t>
@@ -1655,11 +1600,6 @@
           <t>উপরের প্রশ্নে নিজস্ব ওজনে ঝুলন্ত তারটির অভ্যন্তরে সঞ্চিত মোট স্থিতিস্থাপক বিভব শক্তি $U_{\text{total}}$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>নিচের প্রান্ত থেকে $y$ উচ্চতায় টান $T(y) = \frac{Mgy}{L}$ এবং পীড়ন $\sigma(y) = \frac{T(y)}{A} = \frac{Mgy}{AL}$। $dy$ অংশের আয়তন $dV = A dy$। ওই অংশে সঞ্চিত শক্তি $dU = \frac{\sigma(y)^2}{2Y}dV = \frac{1}{2Y}\left(\frac{Mgy}{AL}\right)^2 A dy = \frac{M^2 g^2}{2 Y A L^2}y^2 dy$। সমগ্র তারের জন্য সমাকলন করি: $U_{\text{total}} = \int_0^L \frac{M^2 g^2}{2 Y A L^2}y^2 dy = \frac{M^2 g^2}{2 Y A L^2}\left[\frac{y^3}{3}\right]_0^L = \frac{M^2 g^2 L}{6 Y A}$। লক্ষণীয় যে এটি $\frac{1}{3}(Mg \Delta L)$-এর সমান।</t>
@@ -1705,11 +1645,6 @@
           <t>$L$ দৈর্ঘ্য ও $A$ প্রস্থচ্ছেদের একটি ধাতব তারকে দুটি অনড় স্থির দেয়ালের মাঝে টানটান করে আটকানো হলো। তারের উপাদানের রৈখিক প্রসারণ সহগ $\alpha$ এবং ইয়ং-এর গুণাঙ্ক $Y$। তাপমাত্রা $\Delta T$ কমানো হলে তারে সৃষ্ট তাপীয় পীড়ন এবং দেয়ালের ওপর প্রযুক্ত বল কত?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>তাপমাত্রা $\Delta T$ হ্রাস পেলে অবাধ প্রসারণের ক্ষেত্রে তারটি $\Delta L_{\text{thermal}} = L \alpha \Delta T$ সংকুচিত হতো। কিন্তু দেয়াল দুটি অনড় হওয়ায় তারটির দৈর্ঘ্য পরিবর্তন হতে পারে না ($\Delta L_{\text{net}} = 0$)। ফলে দেয়াল তারটিকে প্রসারিত রেখে তার ভেতর তাপীয় প্রসার্য পীড়ন (Thermal Tensile Stress) সৃষ্টি করে। উৎপন্ন তাপীয় বিকৃতি $\epsilon = \frac{\Delta L_{\text{thermal}}}{L} = \alpha \Delta T$। হুকের সূত্রানুসারে তাপীয় পীড়ন $\sigma = Y \epsilon = Y \alpha \Delta T$। দেয়ালের ওপর তার কর্তৃক প্রযুক্ত মোট টান বল $F = \sigma A = Y A \alpha \Delta T$। লক্ষণীয় যে এই বল তারের আদি দৈর্ঘ্য $L$-এর ওপর নির্ভর করে না।</t>
@@ -1755,11 +1690,6 @@
           <t>$2L$ দূরত্বের দুটি অনড় খুঁটির মাঝে টানটান অনুভূমিক অবস্থায় বাঁধা একটি তারের তাপমাত্রা সামান্য $\Delta T$ বৃদ্ধি পেলে তারটির মধ্যবিন্দু উল্লম্বভাবে $y$ পরিমাণ নিচে ঝুলে পড়ে। জ্যামিতিক বিকৃতি বিশ্লেষণ করে মধ্যবিন্দুর ঝুলন $y$-এর সমীকরণ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>তারের আদি দৈর্ঘ্য $2L$। তাপমাত্রা বৃদ্ধিতে প্রসারিত দৈর্ঘ্য $2L' = 2L(1 + \alpha \Delta T) \implies L' = L(1 + \alpha \Delta T)$। পিথাগোরাসের উপপাদ্য অনুসারে সমকোণী ত্রিভুজ থেকে: $L'^2 = L^2 + y^2 \implies L^2(1 + \alpha \Delta T)^2 = L^2 + y^2$। দ্বিপদী বিস্তার করি ($(\alpha \Delta T)^2 \approx 0$): $L^2(1 + 2\alpha \Delta T) = L^2 + y^2 \implies L^2 + 2L^2\alpha \Delta T = L^2 + y^2 \implies y^2 = 2L^2\alpha \Delta T \implies y = L\sqrt{2\alpha \Delta T}$। এটি নির্দেশ করে যে অতি ক্ষুদ্র রৈখিক প্রসারণের জন্যও মধ্যবিন্দুর উল্লম্ব ঝুলন অপেক্ষাকৃত অনেক বেশি বৃদ্ধি পায় কারণ $y \propto \sqrt{\Delta T}$।</t>
@@ -1805,11 +1735,6 @@
           <t>$A$ প্রস্থচ্ছেদের একটি উল্লম্ব হালকা তারের মুক্ত প্রান্তে $m$ ভরের একটি ব্লককে (ক) ধীরে ধীরে নামিয়ে সাম্যাবস্থায় আনা হলো এবং (খ) তারটির অপ্রসারিত অবস্থায় হাত সরিয়ে হঠাৎ ছেড়ে দেওয়া হলো। উভয় ক্ষেত্রে তারে উৎপন্ন সর্বোচ্চ পীড়নের অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>(ক) ধীরে ধীরে স্থাপন করলে সাম্যাবস্থায় তারের টান ওজনের সমান: $T_1 = mg$। ফলে স্থৈতিক পীড়ন $\sigma_1 = \frac{mg}{A}$ এবং প্রসারণ $x_1 = \frac{mgL}{YA}$। (খ) হঠাৎ ছেড়ে দিলে ব্লকটি একটি উল্লম্ব স্প্রিং-ব্লক সরল ছন্দিত গতিতে দুলতে শুরু করে। সর্বোচ্চ প্রসারণ $x_{\max}$-এ গতিশক্তি সাময়িকভাবে শূন্য হয়। কাজ-শক্তি উপপাদ্য: মহাকর্ষীয় বিভব শক্তি হ্রাস = স্থিতিস্থাপক স্থিতিশক্তি বৃদ্ধি $\implies mg x_{\max} = \frac{1}{2}\left(\frac{YA}{L}\right)x_{\max}^2 \implies x_{\max} = \frac{2mgL}{YA} = 2x_1$। সর্বোচ্চ প্রসারণে তারের সর্বোচ্চ টান $T_{\max} = \frac{YA}{L}x_{\max} = 2mg$। ফলে সর্বোচ্চ গতিশীল পীড়ন $\sigma_2 = \frac{2mg}{A} = 2\sigma_1$। অতএব হঠাৎ ছেড়ে দিলে উৎপন্ন সর্বোচ্চ পীড়ন স্থৈতিক পীড়নের ঠিক দ্বিগুণ হয়।</t>
@@ -1855,11 +1780,6 @@
           <t>$L$ দৈর্ঘ্য ও $\rho$ ঘনত্বের একটি ধাতব তারকে $Y$ ইয়ং-এর গুণাঙ্কে টান পীড়ন $\sigma$ দিয়ে প্রসারিত রাখা হয়েছে। তারটি হঠাৎ বিচ্ছিন্ন বা ছিঁড়ে গেলে তারের সম্পূর্ণ সঞ্চিত স্থিতিস্থাপক শক্তি যদি সমভাবে তাপে রূপান্তরিত হয়, তবে তারটির তাপমাত্রা বৃদ্ধি $\Delta T$ কত হবে? (উপাদানের আপেক্ষিক তাপ $s$)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>তারের প্রতি একক আয়তনে সঞ্চিত স্থিতিস্থাপক শক্তি $u = \frac{\sigma^2}{2Y}$। তারটির ভর $m = \rho V$। তারটিতে মোট সঞ্চিত স্থিতিস্থাপক শক্তি $U = u V = \frac{\sigma^2 V}{2Y}$। সম্পূর্ণ শক্তি তাপে রূপান্তরিত হলে তাপীয় সমীকরণ: $Q = U \implies m s \Delta T = \frac{\sigma^2 V}{2Y} \implies (\rho V) s \Delta T = \frac{\sigma^2 V}{2Y}$। উভয় পাশ থেকে আয়তন $V$ বর্জন করে পাই: $\rho s \Delta T = \frac{\sigma^2}{2Y} \implies \Delta T = \frac{\sigma^2}{2 Y \rho s}$।</t>
@@ -1905,11 +1825,6 @@
           <t>সমান পুরুত্ব $t$ বিশিষ্ট দুটি ভিন্ন ধাতুর পাত (যাদের ইয়ং-এর গুণাঙ্ক সমান কিন্তু রৈখিক প্রসারণ সহগ $\alpha_1$ ও $\alpha_2$, $\alpha_1 &gt; \alpha_2$) রিভেটিং করে একটি দ্বি-ধাতব পাত তৈরি করা হলো। তাপমাত্রা $\Delta T$ বৃদ্ধি পেলে পাতটির বক্রতা ব্যাসার্ধ $R$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>উভয় পাতের যৌথ পুরুত্ব $2t$। বক্ররেখার কেন্দ্র থেকে প্রথম পাতের মধ্যরেখার ব্যাসার্ধ $R - t/2$ এবং দ্বিতীয় পাতের $R + t/2$। উভয়ের প্রসারণ পার্থক্য: $\Delta L_1 - \Delta L_2 = L_0(\alpha_1 - \alpha_2)\Delta T$। আবার জ্যামিতিকভাবে কোণ $\theta$ হলে $L_1 = \theta(R + t/2)$ এবং $L_2 = \theta(R - t/2)$, ফলে $L_1 - L_2 = \theta t$ এবং গড় দৈর্ঘ্য $L_0 \approx R\theta$। দুটি সমন্বয় করে পাই: $R\theta(\alpha_1 - \alpha_2)\Delta T = \theta t \implies R = \frac{t}{(\alpha_1 - \alpha_2)\Delta T}$। ইয়ং-এর গুণাঙ্ক ভিন্ন হলে টিমশেঙ্কোর পূর্ণাঙ্গ সূত্র প্রযোজ্য।</t>
@@ -1953,11 +1868,6 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>ধাতব তার টানলে এর প্রসারণ মূলত পরমাণুগুলোর মধ্যবর্তী দূরত্বের পরিবর্তনের কারণে ঘটে কিন্তু ভালকানাইজড রাবার প্রসারিত করার চালিকা শক্তি মূলত এনট্রপি পরিবর্তন। রাবার ব্যান্ডকে দ্রুত টেনে প্রসারিত করে ঠোঁটে স্পর্শ করলে তা উষ্ণ অনুভূত হয় কেন?</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2053,11 +1963,6 @@
           <t>$R$ ব্যাসার্ধ ও $L$ দৈর্ঘ্যের একটি আনুভূমিক বৃত্তাকার কৈশিক নলের দুই প্রান্তে চাপ পার্থক্য $P$ বজায় রাখলে সান্দ্রতা গুণাঙ্ক $\eta$-এর তরলের জন্য প্রতি সেকেন্ডে নির্গত তরলের আয়তন $Q = \frac{\pi P R^4}{8\eta L}$ প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>নলের অক্ষ থেকে $r$ ব্যাসার্ধ এবং $L$ দৈর্ঘ্যের একটি সিলিন্ডারীয় তরল কলাম বিবেচনা করি। কলামের দুই প্রান্তের চাপ বল $F_p = P \pi r^2$। এই বল পার্শ্বীয় সান্দ্র বল দ্বারা প্রতিহত হয়: $F_\eta = -\eta (2\pi r L)\frac{dv}{dr}$। ভারসাম্যে: $P \pi r^2 = -2\pi \eta r L \frac{dv}{dr} \implies \frac{dv}{dr} = -\frac{P}{2\eta L} r$। সমাকলন করি প্রাচীরে নো-স্লিপ বাউন্ডারি শর্ত ($v(R) = 0$) দিয়ে: $v(r) = \frac{P}{4\eta L}(R^2 - r^2)$ (প্যারাবলিক বেগ প্রোফাইল)। $r$ থেকে $r+dr$ অঞ্চলের মধ্য দিয়ে প্রবাহের হার $dQ = v(r) 2\pi r dr = \frac{2\pi P}{4\eta L}(R^2 r - r^3)dr$। সমগ্র নলে সমাকলন করি: $Q = \int_0^R \frac{\pi P}{2\eta L}(R^2 r - r^3)dr = \frac{\pi P}{2\eta L}\left[\frac{R^4}{2} - \frac{R^4}{4}\right] = \frac{\pi P R^4}{8\eta L}$।</t>
@@ -2103,11 +2008,6 @@
           <t>একই দৈর্ঘ্যের দুটি কৈশিক নলের ব্যাসার্ধ যথাক্রমে $r_1$ ও $r_2$। নল দুটিকে (ক) শ্রেণি সমবায়ে এবং (খ) সমান্তরাল সমবায়ে যুক্ত করে দুই প্রান্তে মোট চাপ পার্থক্য $P$ প্রয়োগ করলে তাদের তুল্য তরল রোধ (Fluid Resistance) কত?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>পয়সিলির সূত্র ওহমের সূত্রের সাদৃশ্য: $P = Q R_{\text{fluid}}$ যেখানে তরল রোধ $R_f = \frac{8\eta L}{\pi r^4} \propto \frac{1}{r^4}$। (ক) শ্রেণি সমবায়ে উভয় নলের মধ্য দিয়ে একই প্রবাহ $Q$ যায় এবং চাপ ভাগ হয়: $R_{f,\text{series}} = R_{f1} + R_{f2} = \frac{8\eta L}{\pi}\left(\frac{1}{r_1^4} + \frac{1}{r_2^4}\right)$। (খ) সমান্তরাল সমবায়ে উভয় নলে চাপ সমান ($P$) এবং মোট প্রবাহ যোগ হয়: $\frac{1}{R_{f,\text{parallel}}} = \frac{1}{R_{f1}} + \frac{1}{R_{f2}} = \frac{\pi}{8\eta L}(r_1^4 + r_2^4) \implies R_{f,\text{parallel}} = \frac{8\eta L}{\pi(r_1^4 + r_2^4)}$।</t>
@@ -2153,11 +2053,6 @@
           <t>রেইনল্ডস সংখ্যা $Re = \frac{\rho v D}{\eta}$ জড়তা বল এবং সান্দ্র বলের অনুপাত নির্দেশ করে। $Re &lt; 2000$ এবং $Re &gt; 4000$-এর জন্য প্রবাহের প্রকৃতি কেমন হয় এবং রক্তের ধমনীতে অ্যাথেরোস্ক্লেরোসিসের ফলে টার্বুলেন্স সৃষ্টির কারণ কী?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>রেইনল্ডস সংখ্যার ভৌত অর্থ: জড়তা বল $\sim \rho v^2 D^2$ এবং সান্দ্র বল $\sim \eta v D$, ফলে অনুপাত $\frac{F_{\text{inertia}}}{F_{\text{viscous}}} = \frac{\rho v D}{\eta} = Re$। (১) $Re &lt; 2000$ হলে সান্দ্র বল প্রবল থাকে এবং তরল শান্ত সমান্তরাল স্তরে প্রবাহিত হয় (ল্যামিনার প্রবাহ)। (২) $Re &gt; 4000$ হলে জড়তা বল সান্দ্রতাকে ছাপিয়ে বিশৃঙ্খল ঘূর্ণি ও এডি কারেন্ট সৃষ্টি করে (টার্বুলেন্ট প্রবাহ)। ধমনীতে কোলেস্টেরল জমার কারণে নালীর ব্যাস $D$ সংকুচিত হলে তরল ধারাবাহিকতার সমীকরণ অনুসারে রক্তের বেগ $v$ নাটকীয়ভাবে বৃদ্ধি পায় ($v \propto 1/D^2$), ফলে $Re \propto v D \propto 1/D$ বৃদ্ধি পেয়ে ২০০০ অতিক্রম করে এবং রক্তে টার্বুলেন্ট প্রবাহ ও মারমার (Murmur) শব্দের সৃষ্টি করে।</t>
@@ -2203,11 +2098,6 @@
           <t>$R_1$ ও $R_2$ ব্যাসার্ধের ($R_2 &gt; R_1$) দুটি দীর্ঘ সমকেন্দ্রিক সিলিন্ডারের মধ্যবর্তী ফাঁকা অংশ $\eta$ সান্দ্রতার তরল দ্বারা পূর্ণ। অভ্যন্তরীণ সিলিন্ডারটিকে স্থির রেখে বাইরের সিলিন্ডারটিকে $\omega$ ধ্রুব কৌণিক বেগে ঘোরাতে প্রয়োজনীয় টর্ক $\tau$ নির্ণয় কর (সিলিন্ডারের দৈর্ঘ্য $L$)।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>কেন্দ্র থেকে $r$ ব্যাসার্ধের তরল স্তরের বেগ $v = \omega(r) r$। বেগ গ্রেডিয়েন্ট $\frac{dv}{dr} - \frac{v}{r} = r \frac{d\omega}{dr}$। সান্দ্র পীড়ন $\tau_{\text{shear}} = \eta r \frac{d\omega}{dr}$। ক্ষেত্রফল $A = 2\pi r L$। অক্ষ সাপেক্ষে সান্দ্র টর্ক: $\tau = (2\pi r L)(\tau_{\text{shear}}) r = 2\pi \eta L r^3 \frac{d\omega}{dr}$। স্থিতাবস্থায় সকল স্তরে টর্ক সমান। সমাকলন করি: $\int_0^\omega d\omega = \frac{\tau}{2\pi \eta L}\int_{R_1}^{R_2} \frac{dr}{r^3} \implies \omega = \frac{\tau}{2\pi \eta L}\left[-\frac{1}{2r^2}\right]_{R_1}^{R_2} = \frac{\tau}{4\pi \eta L}\left(\frac{1}{R_1^2} - \frac{1}{R_2^2}\right)$। অতএব প্রয়োজনীয় টর্ক $\tau = \frac{4\pi \eta L \omega}{\frac{1}{R_1^2} - \frac{1}{R_2^2}} = \frac{4\pi \eta L \omega R_1^2 R_2^2}{R_2^2 - R_1^2}$।</t>
@@ -2261,7 +2151,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>(১) তরলের ক্ষেত্রে: সান্দ্রতার প্রধান কারণ হলো প্রতিবেশী অণুসমূহের মধ্যকার আন্তঃআণবিক আকর্ষণ বল (Cohesive force)। তাপমাত্রা বৃদ্ধি পেলে অণুগুলোর তাপীয় গতিশক্তি বৃদ্ধি পায়, ফলে আন্তঃআণবিক বন্ধন দুর্বল হয়ে অণুগুলোর একে অপরকে অতিক্রম করে চলাচল সহজ হয়; ফলে তরলের সান্দ্রতা দ্রুত হ্রাস পায় ($\eta_{	ext{liquid}} \propto e^{E_a/k_B T}$)। (২) গ্যাসের ক্ষেত্রে: আন্তঃআণবিক আকর্ষণ নগণ্য; সান্দ্রতার প্রধান কারণ হলো ভিন্ন বেগের স্তরের মধ্যে অণুসমূহের স্থানান্তরের মাধ্যমে ভরবেগের পরিবহন। তাপমাত্রা বৃদ্ধি পেলে গ্যাসের অণুসমূহের মূল-গড়-বর্গ বেগ $v_{	ext{rms}} \propto \sqrt{T}$ বৃদ্ধি পায়, ফলে স্তরগুলোর মধ্যে দ্রুত ভরবেগ বিনিময় ঘটে এবং গ্যাসের সান্দ্রতা বৃদ্ধি পায় ($\eta_{	ext{gas}} \propto \sqrt{T}$)।</t>
+          <t>(১) তরলের ক্ষেত্রে: সান্দ্রতার প্রধান কারণ হলো প্রতিবেশী অণুসমূহের মধ্যকার আন্তঃআণবিক আকর্ষণ বল (Cohesive force)। তাপমাত্রা বৃদ্ধি পেলে অণুগুলোর তাপীয় গতিশক্তি বৃদ্ধি পায়, ফলে আন্তঃআণবিক বন্ধন দুর্বল হয়ে অণুগুলোর একে অপরকে অতিক্রম করে চলাচল সহজ হয়; ফলে তরলের সান্দ্রতা দ্রুত হ্রাস পায় ($\eta_{\text{liquid}} \propto e^{E_a/k_B T}$)। (২) গ্যাসের ক্ষেত্রে: আন্তঃআণবিক আকর্ষণ নগণ্য; সান্দ্রতার প্রধান কারণ হলো ভিন্ন বেগের স্তরের মধ্যে অণুসমূহের স্থানান্তরের মাধ্যমে ভরবেগের পরিবহন। তাপমাত্রা বৃদ্ধি পেলে গ্যাসের অণুসমূহের মূল-গড়-বর্গ বেগ $v_{\text{rms}} \propto \sqrt{T}$ বৃদ্ধি পায়, ফলে স্তরগুলোর মধ্যে দ্রুত ভরবেগ বিনিময় ঘটে এবং গ্যাসের সান্দ্রতা বৃদ্ধি পায় ($\eta_{\text{gas}} \propto \sqrt{T}$)।</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2304,11 +2194,6 @@
           <t>$R$ ব্যাসার্ধের নলে পয়সিলি ল্যামিনার প্রবাহে অক্ষ বরাবর তরলের বেগ সর্বাধিক ($v_{\max}$) এবং নলের সম্পূর্ণ প্রস্থচ্ছেদের গড় বেগ $\bar{v}$ হলে প্রমাণ কর যে $\bar{v} = \frac{1}{2}v_{\max}$।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>প্যারাবলিক বেগ সমীকরণ $v(r) = v_{\max}\left(1 - \frac{r^2}{R^2}\right)$, যেখানে অক্ষের বেগ $v_{\max} = \frac{P R^2}{4\eta L}$। মোট আয়তন প্রবাহ হার $Q = \frac{\pi P R^4}{8\eta L}$। প্রস্থচ্ছেদের ক্ষেত্রফল $A = \pi R^2$। নলের গড় বেগ হলো মোট প্রবাহ হারকে মোট ক্ষেত্রফল দ্বারা ভাগফল: $\bar{v} = \frac{Q}{A} = \frac{\frac{\pi P R^4}{8\eta L}}{\pi R^2} = \frac{P R^2}{8\eta L}$। উভয় বেগের অনুপাত: $\frac{\bar{v}}{v_{\max}} = \frac{\frac{P R^2}{8\eta L}}{\frac{P R^2}{4\eta L}} = \frac{1}{2}$। অতএব গড় বেগ হলো অক্ষীয় সর্বোচ্চ বেগের ঠিক অর্ধেক।</t>
@@ -2354,11 +2239,6 @@
           <t>যদি একজন হৃদরোগীর করোনারি ধমনী কোলেস্টেরল জমার কারণে তার স্বাভাবিক ব্যাসার্ধের ১০% সংকুচিত হয় ($r' = 0.9 r$), তবে একই রক্ত প্রবাহ বজায় রাখতে হৃৎপিণ্ডকে কত শতাংশ অতিরিক্ত রক্তচাপ সৃষ্টি করতে হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>পয়সিলির সূত্র অনুসারে রক্ত প্রবাহ হার $Q = \frac{\pi P r^4}{8\eta L} \implies P \propto \frac{1}{r^4}$। ধমনীর নতুন ব্যাসার্ধ $r' = 0.9 r$। নতুন প্রয়োজনীয় চাপ $P' = P \left(\frac{r}{r'}\right)^4 = P \left(\frac{1}{0.9}\right)^4 = P \left(\frac{1}{0.6561}\right) \approx 1.524 P$। রক্তের চাপ বৃদ্ধি $\Delta P = P' - P \approx 0.524 P = 52.4\%$। অর্থাৎ ধমনী মাত্র ১০% সংকুচিত হলেও রক্তের প্রবাহ ঠিক রাখতে হৃৎপিণ্ডকে ৫০%-এরও বেশি অতিরিক্ত রক্তচাপ প্রয়োগ করতে হয়, যা উচ্চ রক্তচাপ ও হার্ট অ্যাটাকের প্রধান কারণ।</t>
@@ -2404,11 +2284,6 @@
           <t>$\alpha$ নতি কোণের একটি প্রশস্ত মসৃণ হেলানো তল বরাবর $h$ সুষম পুরুত্বের একটি সান্দ্র তরল স্তর অভিকর্ষের অধীনে ল্যামিনার প্রবাহে প্রবাহিত হচ্ছে। মুক্ত তলে সান্দ্র পীড়ন শূন্য ধরে তল থেকে $y$ দূরত্বের বেগের সমীকরণ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>হেলানো তলের সমান্তরালে ওজনের উপাংশ $\rho g \sin\alpha$। সান্দ্র বলের সমীকরণ: $\frac{d\tau}{dy} = -\rho g\sin\alpha \implies \tau(y) = \rho g\sin\alpha (h - y)$ (যেহেতু মুক্ত তল $y=h$-তে বাতাসজনিত পীড়ন $\tau=0$)। নিউটনের সান্দ্রতা সূত্র: $\tau(y) = \eta \frac{dv}{dy}$। অতএব $\eta \frac{dv}{dy} = \rho g\sin\alpha (h - y) \implies \frac{dv}{dy} = \frac{\rho g\sin\alpha}{\eta}(h - y)$। হেলানো তলের মেঝেতে নো-স্লিপ বাউন্ডারি শর্ত ($y=0$-তে $v=0$) প্রয়োগ করে সমাকলন করি: $v(y) = \frac{\rho g\sin\alpha}{\eta}\left(hy - \frac{y^2}{2}\right)$। মুক্ত তলে ($y=h$) বেগ সর্বাধিক: $v_{\max} = \frac{\rho g h^2 \sin\alpha}{2\eta}$।</t>
@@ -2454,11 +2329,6 @@
           <t>নিউটনের সান্দ্রতার সূত্র $F = -\eta A \frac{dv}{dz}$ থেকে সান্দ্রতা গুণাঙ্ক $\eta$-এর মাত্রা এবং এসআই একক ও সিজিএস এককের (Poise) মধ্যে সম্পর্ক প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>সমীকরণ থেকে সান্দ্রতা গুণাঙ্ক $\eta = \frac{F}{A \frac{dv}{dz}}$। বলের মাত্রা $[F] = \text{MLT}^{-2}$, ক্ষেত্রফলের মাত্রা $[A] = \text{L}^2$, এবং বেগ গ্রেডিয়েন্টের মাত্রা $\left[\frac{dv}{dz}\right] = \frac{\text{LT}^{-1}}{\text{L}} = \text{T}^{-1}$। অতএব সান্দ্রতার মাত্রা $[\eta] = \frac{\text{MLT}^{-2}}{\text{L}^2 \cdot \text{T}^{-1}} = \text{ML}^{-1}\text{T}^{-1}$। এসআই একক: $\text{N}\cdot\text{s/m}^2$ বা $\text{Pa}\cdot\text{s}$ বা $\text{kg}/(\text{m}\cdot\text{s})$। সিজিএস একক: $\text{dyne}\cdot\text{s/cm}^2 = \text{Poise}$ (পয়েজ)। রূপান্তর: $1\text{ Pa}\cdot\text{s} = \frac{1\text{ N}\cdot\text{s}}{\text{m}^2} = \frac{10^5\text{ dynes}\cdot\text{s}}{(10^2\text{ cm})^2} = \frac{10^5}{10^4}\text{ Poise} = 10\text{ Poise}$।</t>
@@ -2504,11 +2374,6 @@
           <t>সান্দ্র তরল প্রবাহে সান্দ্র বলের বিরুদ্ধে কাজ করার ফলে যান্ত্রিক শক্তি চিরতরে তাপে অপচয় হয়। এক-মাত্রিক শিয়ার প্রবাহে প্রতি একক আয়তনে প্রতি সেকেন্ডে উৎপন্ন তাপীয় শক্তির হার $\frac{dE_{\text{diss}}}{dt dV}$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>ক্ষুদ্র তরল উপাদানের ওপর সান্দ্র পীড়ন $\tau = \eta \frac{dv}{dy}$। ক্ষুদ্র সময় $dt$-তে কৃন্তন বিকৃতি $d\gamma = \left(\frac{dv}{dy}\right)dt$। প্রতি একক আয়তনে কৃতকাজ $dW_{\text{visc}} = \tau d\gamma = \left(\eta \frac{dv}{dy}\right)\left(\frac{dv}{dy}dt\right) = \eta \left(\frac{dv}{dy}\right)^2 dt$। অতএব প্রতি সেকেন্ডে প্রতি একক আয়তনে উৎপন্ন তাপীয় শক্তির হার: $\Phi = \frac{dW_{\text{visc}}}{dt dV} = \eta \left(\frac{dv}{dy}\right)^2$। যেহেতু এই রাশিটি সর্বদা বেগের গ্রেডিয়েন্টের বর্গের সমানুপাতিক, সেহেতু প্রবাহের অভিমুখ যাই হোক না কেন, $\Phi \ge 0$ সর্বদা ধনাত্মক থাকে, যা তাপগতিবিদ্যার দ্বিতীয় সূত্রানুসারে যান্ত্রিক শক্তির অপ্রত্যাবর্তী তাপীয় রূপান্তর নির্দেশ করে।</t>
@@ -2554,11 +2419,6 @@
           <t>সান্দ্র মাধ্যমে ধীরগতিতে গতিশীল একটি ক্ষুদ্র গোলকের ওপর ক্রিয়াশীল সান্দ্র ড্র্যাগ বল $F_d$ তরলের সান্দ্রতা গুণাঙ্ক $\eta$, গোলকের ব্যাসার্ধ $r$ এবং বেগ $v$-এর ওপর নির্ভর করে। মাত্রিক বিশ্লেষণ ও সীমানা শর্ত দ্বারা $F_d = 6\pi\eta r v$ প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>ধরা যাক $F_d = k \eta^a r^b v^c$। মাত্রা সমীকরণ: $[F_d] = \text{MLT}^{-2}$, $[\eta] = \text{ML}^{-1}\text{T}^{-1}$, $[r] = \text{L}$, $[v] = \text{LT}^{-1}$। সমতা করি: $\text{MLT}^{-2} = (\text{ML}^{-1}\text{T}^{-1})^a (\text{L})^b (\text{LT}^{-1})^c = \text{M}^a \text{L}^{-a + b + c} \text{T}^{-a - c}$। ঘাত সমীকরণ: $a = 1$; $-a - c = -2 \implies c = 2 - 1 = 1$; $-a + b + c = 1 \implies -1 + b + 1 = 1 \implies b = 1$। ফলে $F_d = k \eta r v$। নেভিয়ার-স্টোকস সমীকরণের ল্যামিনার ক্রিমিং প্রবাহ সমাধান ($Re \ll 1$) থেকে সার্বজনীন সমানুপাতিক ধ্রুবক $k = 6\pi$ প্রাপ্ত হয়। ফলে $F_d = 6\pi\eta r v$।</t>
@@ -2604,11 +2464,6 @@
           <t>$\rho$ ঘনত্বের একটি ক্ষুদ্র কঠিন গোলক (ব্যাসার্ধ $r$) $\sigma$ ঘনত্বের এবং $\eta$ সান্দ্রতা বিশিষ্ট একটি সান্দ্র তরলের মধ্য দিয়ে মুক্তভাবে পড়ছে। গোলকটির প্রান্তিক বেগ (Terminal Velocity $v_t$) প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>গোলকটির ওপর তিনটি বল কাজ করে: (১) নিম্নমুখী ওজন $W = \frac{4}{3}\pi r^3 \rho g$। (২) ঊর্ধ্বমুখী প্লবতা বল $F_b = \frac{4}{3}\pi r^3 \sigma g$। (৩) ঊর্ধ্বমুখী সান্দ্র ড্র্যাগ বল $F_d = 6\pi\eta r v$। যখন গোলকটি প্রান্তিক বেগ $v_t$-তে পৌঁছায়, তখন লব্ধি বল শূন্য হয়: $W = F_b + F_d \implies \frac{4}{3}\pi r^3 \rho g = \frac{4}{3}\pi r^3 \sigma g + 6\pi\eta r v_t \implies 6\pi\eta r v_t = \frac{4}{3}\pi r^3 (\rho - \sigma)g \implies v_t = \frac{2 r^2 (\rho - \sigma)g}{9\eta}$। লক্ষণীয় যে প্রান্তিক বেগ ব্যাসার্ধের বর্গের সমানুপাতিক ($v_t \propto r^2$)।</t>
@@ -2654,11 +2509,6 @@
           <t>একটি সান্দ্র তরলে ($\sigma = 1.2\text{ g/cm}^3, \eta = 0.8\text{ Pa}\cdot\text{s}$) একটি ক্ষুদ্র বায়ু বুদবুদ ($r = 1\text{ mm}$, বায়ুর ঘনত্ব নগণ্য) ঊর্ধ্বমুখী প্রান্তিক বেগে উঠছে। বুদবুদটির প্রান্তিক দ্রুতি কত? ($g = 9.8\text{ m/s}^2$)</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>বায়ুর ঘনত্ব $\rho \approx 0$ হওয়ায় কার্যকর ঘনত্ব পার্থক্য $\rho - \sigma = -\sigma = -1200\text{ kg/m}^3$। ঋণাত্মক চিহ্ন ঊর্ধ্বমুখী গতি নির্দেশ করে। বুদবুদের ব্যাসার্ধ $r = 10^{-3}\text{ m}$। সান্দ্রতা $\eta = 0.8\text{ Pa}\cdot\text{s}$। প্রান্তিক দ্রুতির মান: $v_t = \frac{2 r^2 \sigma g}{9\eta} = \frac{2(10^{-3})^2 (1200)(9.8)}{9(0.8)} = \frac{2 \times 10^{-6} \times 11760}{7.2} = \frac{0.02352}{7.2} \approx 3.27 \times 10^{-3}\text{ m/s} = 3.27\text{ mm/s}$।</t>
@@ -2704,11 +2554,6 @@
           <t>মিলিকানের তেল বিন্দু পরীক্ষায় বৈদ্যুতিক ক্ষেত্রের অনুপস্থিতিতে $r$ ব্যাসার্ধের একটি তেল বিন্দু $v_1$ প্রান্তিক বেগে নিচে পড়ে। উল্লম্ব ঊর্ধ্বমুখী বৈদ্যুতিক ক্ষেত্র $E$ প্রয়োগ করলে এটি $v_2$ বেগে ওপরের দিকে ওঠে। তেল বিন্দুর আধান $q$ নির্ণয়ের সমীকরণ প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>(১) ক্ষেত্রহীন অবস্থায়: নিম্নমুখী ওজনের সমান সান্দ্র বল $6\pi\eta r v_1 = m_{\text{eff}} g$ (প্লবতা সহ)। (২) ঊর্ধ্বমুখী গতির ক্ষেত্রে: বৈদ্যুতিক বল ওজনের চেয়ে বেশি, ফলে লব্ধি ঊর্ধ্বমুখী বল সান্দ্র বলের সমান: $q E - m_{\text{eff}} g = 6\pi\eta r v_2 \implies q E = m_{\text{eff}} g + 6\pi\eta r v_2 = 6\pi\eta r v_1 + 6\pi\eta r v_2 = 6\pi\eta r (v_1 + v_2)$। অতএব তেল বিন্দুর আধান $q = \frac{6\pi\eta r (v_1 + v_2)}{E}$। প্রথম সমীকরণ থেকে ব্যাসার্ধ $r = \sqrt{\frac{9\eta v_1}{2(\rho - \sigma)g}}$ নির্ণয় করে $q$-এর মান সরাসরি পরিমাপ করা হয়।</t>
@@ -2754,11 +2599,6 @@
           <t>একই আকারের আটটি তরল ফোঁটা বাতাসে প্রতিটি $v_0$ প্রান্তিক বেগে পড়ছিল। ফোঁটাগুলো একত্রিত হয়ে একটি একক বৃহৎ গোলাকার ফোঁটায় পরিণত হলে নতুন প্রান্তিক বেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>প্রতিটি ক্ষুদ্র ফোঁটার ব্যাসার্ধ $r$ এবং বৃহৎ ফোঁটার ব্যাসার্ধ $R$। আয়তন সংরক্ষণশীলতা: $\frac{4}{3}\pi R^3 = 8 \times \left(\frac{4}{3}\pi r^3\right) \implies R^3 = 8r^3 \implies R = 2r$। স্টোকসের প্রান্তিক বেগের সূত্রানুসারে $v_t \propto r^2$। অতএব বৃহৎ ফোঁটার প্রান্তিক বেগ $V_t = v_0 \left(\frac{R}{r}\right)^2 = v_0 (2)^2 = 4v_0$। অর্থাৎ প্রান্তিক বেগ চারগুণ বৃদ্ধি পাবে। সাধারণ $n$ সংখ্যক ফোঁটার জন্য $V_t = n^{2/3}v_0$।</t>
@@ -2804,11 +2644,6 @@
           <t>$m$ ভরের একটি ক্ষুদ্র কণা স্থির অবস্থা থেকে সান্দ্র তরলে ফেলা হলো। সান্দ্র ড্র্যাগ বল $F_d = -kv$ হলে সময়ের অপেক্ষক হিসেবে বেগ $v(t)$ এবং রিল্যাক্সেশন টাইম $\tau$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>গতির সমীকরণ: $m\frac{dv}{dt} = m g_{\text{eff}} - kv \implies \frac{dv}{dt} + \frac{k}{m}v = g_{\text{eff}}$। রিল্যাক্সেশন সময় $\tau = \frac{m}{k}$ এবং প্রান্তিক বেগ $v_t = \frac{m g_{\text{eff}}}{k} = g_{\text{eff}}\tau$। ব্যবকলনীয় সমীকরণ সমাধান করে: $\int_0^v \frac{dv}{v_t - v} = \frac{1}{\tau}\int_0^t dt \implies -\ln\left(1 - \frac{v}{v_t}\right) = \frac{t}{\tau} \implies v(t) = v_t(1 - e^{-t/\tau})$। $t = 3\tau$ সময় পর বেগ তার প্রান্তিক বেগের প্রায় $95\%$ এবং $t = 5\tau$ পর $99.3\%$ মানে পৌঁছায়।</t>
@@ -2854,11 +2689,6 @@
           <t>বৃহৎ গোলক বা উচ্চ বেগে পতনের ক্ষেত্রে যখন রেইনল্ডস সংখ্যা $Re &gt; 1000$ হয়, তখন স্টোকসের রৈখিক সূত্র অকার্যকর হয়ে নিউটনের দ্বিঘাত ড্র্যাগ সূত্র $F_d = \frac{1}{2}C_d \rho A v^2$ প্রযোজ্য হয় কেন এবং প্রান্তিক বেগ ব্যাসার্ধের ওপর কীভাবে নির্ভর করে?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>উচ্চ রেইনল্ডস সংখ্যায় সান্দ্র ঘর্ষণের চেয়ে বস্তুর পেছনে সৃষ্ট টার্বুলেন্ট ঘূর্ণি ও চাপের পার্থক্য (Form Drag) প্রবল হয়ে ওঠে। ফলে ড্র্যাগ বল বেগের বর্গের সমানুপাতিক হয়: $F_d = \frac{1}{2}C_d \rho (\pi r^2) v^2$। প্রান্তিক বেগের জন্য: $W = F_d \implies \frac{4}{3}\pi r^3 \rho_s g = \frac{1}{2}C_d \rho \pi r^2 v_t^2 \implies v_t = \sqrt{\frac{8\rho_s g r}{3 C_d \rho}} \propto \sqrt{r}$। লক্ষণীয় যে স্টোকস অঞ্চলে $v_t \propto r^2$, কিন্তু টার্বুলেন্ট নিউটনীয় অঞ্চলে $v_t \propto \sqrt{r}$। প্যারাশুটিস্টদের পতনে এই দ্বিঘাত ড্র্যাগ প্রযোজ্য।</t>
@@ -2904,11 +2734,6 @@
           <t>একটি সান্দ্র তরলের ভেতরে একটি ক্ষুদ্র গোলককে অনুভূমিকভাবে $v_0$ আদি দ্রুতি দিয়ে ছুঁড়ে দেওয়া হলো। মাধ্যাকর্ষণ অগ্রাহ্য করলে গোলকটি সম্পূর্ণ থামার পূর্ব পর্যন্ত মোট কত অনুভূমিক দূরত্ব অতিক্রম করবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>গতির সমীকরণ: $m \frac{dv}{dt} = -6\pi\eta r v = -kv \implies m v \frac{dv}{dx} = -kv \implies m dv = -k dx$। উভয় পাশে সমাকলন করি আদি বেগ $v_0$ থেকে চূড়ান্ত বেগ $v=0$ পর্যন্ত: $m \int_{v_0}^0 dv = -k \int_0^{x_{\max}} dx \implies -m v_0 = -k x_{\max} \implies x_{\max} = \frac{m v_0}{k} = \frac{m v_0}{6\pi\eta r}$। গোলকটির ভর $m = \frac{4}{3}\pi r^3 \rho$ বসালে: $x_{\max} = \frac{\frac{4}{3}\pi r^3 \rho v_0}{6\pi\eta r} = \frac{2\rho r^2 v_0}{9\eta}$। অতএব অসীম সময় লাগলেও মোট অতিক্রান্ত স্টপ দূরত্ব সসীম।</t>
@@ -2954,11 +2779,6 @@
           <t>একটি ক্ষুদ্র গোলক সান্দ্র তরলে তার প্রান্তিক বেগ $v_t$-তে নিচে পড়ছে। প্রতি সেকেন্ডে তরলে উৎপন্ন তাপীয় শক্তির হার (Power Dissipation $P$) গোলকের ব্যাসার্ধ $r$-এর কোন ঘাতের সমানুপাতিক?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>প্রান্তিক বেগে গতিশক্তি ধ্রুব থাকে, ফলে মহাকর্ষীয় বিভব শক্তি হ্রাসের সম্পূর্ণ হারটি সান্দ্র ড্র্যাগ বলের বিরুদ্ধে কাজে ব্যয় হয়ে তাপে পরিণত হয়। ক্ষমতার সমীকরণ: $P = F_d v_t = (6\pi\eta r v_t) v_t = 6\pi\eta r v_t^2$। আমরা জানি প্রান্তিক বেগ $v_t \propto r^2$। মান বসিয়ে পাই: $P \propto r (r^2)^2 = r \cdot r^4 = r^5$। অর্থাৎ প্রান্তিক বেগে পতিত গোলক দ্বারা প্রতি সেকেন্ডে উৎপন্ন তাপীয় ক্ষমতা ব্যাসার্ধের পঞ্চম ঘাতের ($r^5$) সমানুপাতিক! ব্যাসার্ধ দ্বিগুণ হলে তাপ উৎপাদন $2^5 = 32$ গুণ বৃদ্ধি পায়।</t>
@@ -3004,11 +2824,6 @@
           <t>একটি আল্ট্রাসেন্ট্রিফিউজ মেশিনে কণাগুলোকে কেন্দ্র থেকে $R$ দূরত্বে $\omega$ উচ্চ কৌণিক বেগে ঘোরানো হচ্ছে। অভিকর্ষজ ত্বরণ $g$-এর স্থলে সেন্ট্রিফিউগাল ত্বরণ $\omega^2 R$ প্রতিস্থাপন করে কোলয়েড কণার সেডিমেন্টেশন দ্রুতি (Sedimentation Velocity) নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>আল্ট্রাসেন্ট্রিফিউজে কার্যকর কেন্দ্রাতিগ ত্বরণ $g_{\text{eff}} = \omega^2 R$ (যা প্রায় $100,000 g$ পর্যন্ত হতে পারে)। কার্যকর ওজন $W_{\text{eff}} = \frac{4}{3}\pi r^3 (\rho - \sigma)\omega^2 R$। স্টোকসের ড্র্যাগ বল $F_d = 6\pi\eta r v_s$ এর সাথে ভারসাম্য করে পাই: $6\pi\eta r v_s = \frac{4}{3}\pi r^3 (\rho - \sigma)\omega^2 R \implies v_s = \frac{2 r^2 (\rho - \sigma)\omega^2 R}{9\eta}$। সেডিমেন্টেশন সহগ $s = \frac{v_s}{\omega^2 R} = \frac{2r^2(\rho-\sigma)}{9\eta}$ দ্বারা প্রোটিন ও ডিএনএ অণুর আণবিক ভর ও আকার নির্ধারণ করা হয় (Svedberg একক)।</t>
@@ -3054,11 +2869,6 @@
           <t>প্রমাণ কর যে পৃষ্ঠটান $T$ এবং প্রতি একক ক্ষেত্রফলে পৃষ্ঠশক্তি $u_s$ সাংখ্যিক ও মাত্রাগতভাবে অভিন্ন ($T = \frac{W}{\Delta A}$)।</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>$L$ দৈর্ঘ্যের একটি স্লাইডার যুক্ত তারের ইউ-আকৃতির ফ্রেমে একটি তরল ফিল্ম (যেমন সাবান পানি) তৈরি করা হলো। ফিল্মটির দুটি মুক্ত তল থাকে, ফলে মোট দৈর্ঘ্য $2L$। পৃষ্ঠটান বল ভেতরের দিকে টানে: $F = 2TL$। স্লাইডারটিকে ধীরে ধীরে সমবেগে $x$ দূরত্বে টেনে ক্ষেত্রফল বৃদ্ধি করতে বাহ্যিক বল দ্বারা কৃতকাজ: $W = F x = (2TL)x = T(2Lx) = T \Delta A$, যেখানে $\Delta A = 2Lx$ হলো উভয় পৃষ্ঠের মোট বর্ধিত ক্ষেত্রফল। কাজ-শক্তি উপপাদ্য অনুসারে এই বাহ্যিক কাজ পৃষ্ঠীয় অণুসমূহের বিভব শক্তিতে জমা হয়: $\Delta U = W = T \Delta A$। অতএব প্রতি একক ক্ষেত্রফল বৃদ্ধিতে সঞ্চিত পৃষ্ঠ বিভব শক্তি $u_s = \frac{\Delta U}{\Delta A} = T$। পৃষ্ঠটানের মাত্রা $[T] = \frac{\text{MLT}^{-2}}{\text{L}} = \text{MT}^{-2}$ এবং পৃষ্ঠশক্তির মাত্রা $[u_s] = \frac{\text{ML}^2\text{T}^{-2}}{\text{L}^2} = \text{MT}^{-2}$।</t>
@@ -3104,11 +2914,6 @@
           <t>$r$ ব্যাসার্ধের $n$ সংখ্যক সমান জলীয় ফোঁটা একত্রিত হয়ে একটি একক বৃহৎ গোলাকার ফোঁটায় (ব্যাসার্ধ $R$) পরিণত হলো। জলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং আপেক্ষিক তাপ $s$ হলে এই প্রক্রিয়ায় নির্গত পৃষ্ঠশক্তি $\Delta E$ এবং বৃহৎ ফোঁটার তাপমাত্রা বৃদ্ধি $\Delta \theta$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>আয়তন সংরক্ষণ: $\frac{4}{3}\pi R^3 = n \left(\frac{4}{3}\pi r^3\right) \implies R = n^{1/3}r \implies r = \frac{R}{n^{1/3}}$। আদি মোট ক্ষেত্রফল $A_i = n(4\pi r^2) = n \left(4\pi \frac{R^2}{n^{2/3}}\right) = 4\pi R^2 n^{1/3}$। চূড়ান্ত ক্ষেত্রফল $A_f = 4\pi R^2$। ক্ষেত্রফল হ্রাস $\Delta A = A_i - A_f = 4\pi R^2 (n^{1/3} - 1) = 4\pi r^2 (n - n^{2/3})$। নির্গত পৃষ্ঠশক্তি $\Delta E = T \Delta A = 4\pi T R^2(n^{1/3} - 1) = 4\pi T r^2(n - n^{2/3})$। নির্গত শক্তি ফোঁটার তাপে পরিণত হলে: $\Delta E = m s \Delta \theta = \left(\frac{4}{3}\pi R^3 \rho\right)s \Delta \theta$। অতএব তাপমাত্রা বৃদ্ধি $\Delta \theta = \frac{4\pi T R^2(n^{1/3} - 1)}{\frac{4}{3}\pi R^3 \rho s} = \frac{3T}{\rho s}\left(\frac{1}{R} - \frac{1}{r}\right)$ এর পরম মান $\frac{3T}{\rho s}\left(\frac{1}{r} - \frac{1}{R}\right)$।</t>
@@ -3154,11 +2959,6 @@
           <t>$R$ ব্যাসার্ধের একটি পারদ ফোঁটাকে সমআকারের $10^6$ টি ক্ষুদ্র ফোঁটায় চূর্ণ করতে প্রয়োজনীয় বাহ্যিক কাজের মান নির্ণয় কর (পারদের পৃষ্ঠটান $T$)।</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>আয়তন স্থির থাকায় প্রতিটি ক্ষুদ্র ফোঁটার ব্যাসার্ধ $r = \frac{R}{n^{1/3}} = \frac{R}{(10^6)^{1/3}} = \frac{R}{100} = 10^{-2}R$। আদি ক্ষেত্রফল $A_1 = 4\pi R^2$। $10^6$ টি ফোঁটার মোট চূড়ান্ত ক্ষেত্রফল $A_2 = 10^6 \times (4\pi r^2) = 10^6 \times 4\pi (10^{-2}R)^2 = 10^6 \times 4\pi (10^{-4}R^2) = 100(4\pi R^2) = 100 A_1$। ক্ষেত্রফল বৃদ্ধি $\Delta A = A_2 - A_1 = 100 A_1 - A_1 = 99(4\pi R^2) = 396\pi R^2$। প্রয়োজনীয় কৃতকাজ $W = T \Delta A = 396\pi R^2 T$। যেহেতু ক্ষেত্রফল বিপুল বৃদ্ধি পায়, এই কাজ পরিবেশে তাপ শোষণ করে ফোঁটাগুলোকে শীতল করে।</t>
@@ -3204,11 +3004,6 @@
           <t>বাতাসে ভাসমান $r$ ব্যাসার্ধের একটি সাবানের বুদবুদের ব্যাসার্ধ ফুঁ দিয়ে বাড়িয়ে $2r$ করতে কৃতকাজ কত? (সাবান পানির পৃষ্ঠটান $T$)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>সাবানের বুদবুদ একটি ফাঁপা ফিল্ম যার ভেতরের এবং বাইরের দুটি মুক্ত তল বিদ্যমান। আদি মোট ক্ষেত্রফল $A_1 = 2 \times (4\pi r^2) = 8\pi r^2$। চূড়ান্ত ব্যাসার্ধ $2r$ হলে মোট ক্ষেত্রফল $A_2 = 2 \times [4\pi (2r)^2] = 2 \times (16\pi r^2) = 32\pi r^2$। মোট ক্ষেত্রফল বৃদ্ধি $\Delta A = A_2 - A_1 = 32\pi r^2 - 8\pi r^2 = 24\pi r^2$। অতএব প্রয়োজনীয় মোট কৃতকাজ $W = T \Delta A = 24\pi r^2 T$। (তরল ফোঁটার ক্ষেত্রে কেবল একটি তল থাকে, ফলে কাজ হত $12\pi r^2 T$)।</t>
@@ -3254,11 +3049,6 @@
           <t>$L$ দৈর্ঘ্যের একটি ইস্পাতের সূঁচ জলের পৃষ্ঠে না ডুবে অনুভূমিকভাবে ভাসছে। সূঁচটি যাতে জলে ডুবে না যায় তার জন্য সূঁচের সর্বোচ্চ অনুমোদিত ভর $m_{\max}$ নির্ণয় কর (জলের পৃষ্ঠটান $T$)।</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>সূঁচটি জলের ওপর রাখলে তা জলের মুক্ত পৃষ্ঠকে সামান্য অবতল করে। সূঁচের উভয় পাশের স্পর্শতলে পৃষ্ঠটান বল উল্লম্বের সাথে $\theta$ কোণে কাজ করে। প্রতি একক দৈর্ঘ্যে পৃষ্ঠটান বল $T$। সূঁচের উভয় পাশে মোট ঊর্ধ্বমুখী পৃষ্ঠটান বল $F_v = 2 T L \cos\theta$। ঊর্ধ্বমুখী বল সর্বাধিক হয় যখন স্পর্শ কোণ চরম সীমায় উল্লম্বের সমান্তরাল হয় ($\cos\theta = 1$ বা কোণ $\theta = 0^\circ$)। ভারসাম্যে ওজনের সাথে সমতা করে: $m g = 2 T L \cos\theta \le 2 T L \implies m_{\max} = \frac{2 T L}{g}$।</t>
@@ -3304,11 +3094,6 @@
           <t>ল্যাপ্লাসের আণবিক তত্ত্ব অনুসারে পৃষ্ঠটানের মূল উৎপত্তি কী? তরলের অভ্যন্তরে থাকা অণু এবং মুক্ত পৃষ্ঠের অণুর মধ্যে শক্তির পার্থক্য ব্যাখ্যা কর।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>একটি অণুর চারদিকে প্রায় $10^{-9}\text{ m}$ (১ ন্যানোমিটার) ব্যাসার্ধের গোলককে আণবিক প্রভাব গোলক বলা হয়। তরলের গভীরে থাকা একটি অণু তার চারদিকের সকল প্রতিবেশী অণু দ্বারা সব দিক থেকে সমান আকর্ষণ বল অনুভব করে, ফলে লব্ধি আন্তঃআণবিক বল শূন্য হয়। কিন্তু মুক্ত পৃষ্ঠের একটি অণুর প্রভাব গোলকের উপরের অর্ধেকাংশে বাতাসের অণু থাকে যা তরল অণুর তুলনায় অত্যন্ত কম। ফলে পৃষ্ঠের অণুগুলো তরলের ভেতরের দিকে একটি শক্তিশালী নিট নিম্নমুখী আকর্ষণ বল (Cohesive pull) অনুভব করে। কোনো অণুকে অভ্যন্তর থেকে পৃষ্ঠে আনতে এই আন্তঃআণবিক টানের বিরুদ্ধে কাজ করতে হয়, যা পৃষ্ঠীয় অণুর অতিরিক্ত বিভব শক্তি হিসেবে জমা থাকে। সর্বনিম্ন শক্তির স্বাভাবিক প্রবণতার কারণে তরল সর্বদা তার পৃষ্ঠের ক্ষেত্রফল ন্যূনতম রাখতে চায়, যা পৃষ্ঠটান হিসেবে টানটান স্থিতিস্থাপক পর্দার মতো আচরণ করে।</t>
@@ -3354,11 +3139,6 @@
           <t>তাপমাত্রা বৃদ্ধির সাথে পৃষ্ঠটান কেন হ্রাস পায় এবং সংকট তাপমাত্রায় (Critical Temperature $T_c$) পৃষ্ঠটানের মান কত হয়?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>তাপমাত্রা বৃদ্ধি পেলে তরল অণুসমূহের তাপীয় গতিশক্তি বৃদ্ধি পায়, ফলে অণুগুলোর মধ্যবর্তী আন্তঃআণবিক সংহতি বল (Cohesion) দুর্বল হতে থাকে। এতে পৃষ্ঠীয় অণুগুলোর নিট অন্তর্মুখী টান হ্রাস পায় এবং পৃষ্ঠটান রৈখিকভাবে হ্রাস পায়: $T(\theta) = T_0(1 - \alpha \theta)$। এওটভোস নিয়ম অনুসারে মোলার পৃষ্ঠশক্তি তাপমাত্রার সাথে রৈখিকভাবে সম্পর্কিত: $T (M/\rho)^{2/3} = k(T_c - T)$। সংকট তাপমাত্রায় ($T = T_c$) তরল ও তার সম্পৃক্ত বাষ্পের ঘনত্বের পার্থক্য শূন্য হয়ে যায় এবং তরল-গ্যাস বিভেদতল সম্পূর্ণ অদৃশ্য হয়ে যায়। ফলে সংকট তাপমাত্রায় যেকোনো তরলের পৃষ্ঠটান নিখুঁতভাবে শূন্যে ($T = 0$) নেমে আসে।</t>
@@ -3404,11 +3184,6 @@
           <t>$A$ ক্ষেত্রফলের দুটি সমান্তরাল কাঁচের প্লেটের মাঝে $t$ অত্যন্ত ক্ষুদ্র পুরুত্বের একটি পাতলা জলের ফিল্ম রয়েছে। প্লেট দুটিকে টেনে পরস্পরের থেকে আলাদা করতে প্রয়োজনীয় অনুভূমিক বা উল্লম্ব বল $F$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>জলের ফিল্মটির পরিধির মুক্ত তল অবতল মেনিস্কাস গঠন করে যার বক্রতা ব্যাসার্ধ $R_1 = \frac{t}{2\cos\theta} \approx \frac{t}{2}$ (যেহেতু কাঁচ ও বিশুদ্ধ জলের স্পর্শ কোণ $\theta \approx 0^\circ$)। ফিল্মের ভেতরের চাপ বায়ুমণ্ডলীয় চাপ $P_0$ অপেক্ষা ল্যাপ্লাসের সূত্রানুসারে কম: $\Delta P = P_0 - P_{\text{in}} = \frac{T}{R_1} = \frac{T}{t/2} = \frac{2T}{t}$। প্লেটদ্বয়ের বাইরে বায়ুমণ্ডলীয় চাপ $P_0$ এবং ভেতরে $P_0 - \frac{2T}{t}$। ফলে বাইরের বায়ুমণ্ডলীয় চাপের পার্থক্যের কারণে প্লেট দুটি পরস্পরের দিকে বিপুল বলে চেপে থাকে: $F = \Delta P \times A = \frac{2 A T}{t}$। যেহেতু ফিল্মের পুরুত্ব $t$ অত্যন্ত ক্ষুদ্র (যেমন মাইক্রোমিটার), সেহেতু এই আকর্ষণ বল $F$ অত্যন্ত বিশাল হয়।</t>
@@ -3454,11 +3229,6 @@
           <t>একটি সরু পাইপ থেকে অবিচ্ছিন্ন তরল সিলিন্ডারীয় জেট নির্গত হয়ে কিছু দূর যাওয়ার পর স্বয়ংক্রিয়ভাবে গোলাকার ফোঁটায় বিভক্ত হয়ে যায় কেন? সর্বনিম্ন পৃষ্ঠশক্তির নীতি প্রয়োগ করে ব্যাখ্যা কর।</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>সম-আয়তনের সকল সম্ভাব্য ত্রিমাত্রিক জ্যামিতিক আকারের মধ্যে গোলকের পৃষ্ঠের ক্ষেত্রফল সর্বনিম্ন। $R$ ব্যাসার্ধের একটি দীর্ঘ তরল সিলিন্ডারের পৃষ্ঠের ক্ষেত্রফল প্রতি একক আয়তনে $A/V = \frac{2\pi R L}{\pi R^2 L} = \frac{2}{R}$। এটি সম-আয়তনের গোলকে ($R_s = (1.5 R^2 L)^{1/3}$) পরিণত হলে পৃষ্ঠের ক্ষেত্রফল উল্লেখযোগ্যভাবে হ্রাস পায়। পৃষ্ঠটানের স্বাভাবিক প্রবণতা হলো মোট পৃষ্ঠশক্তি $U = T A$ ন্যূনতম করা। রেলি প্রমাণ করেন যে সিলিন্ডারের অক্ষ বরাবর তরঙ্গের তরঙ্গদৈর্ঘ্য যদি পরিধির চেয়ে বড় হয় ($\lambda &gt; 2\pi R$), তবে সামান্য বিঘ্নিত তরঙ্গের বিস্তৃতি স্বতঃস্ফূর্তভাবে বৃদ্ধি পেয়ে সিলিন্ডারটিকে আলাদা আলাদা গোলাকার ফোঁটায় ভেঙে দেয়।</t>
@@ -3539,43 +3309,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ (সমস্যা 1)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[সমস্যা 1: ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ]
-##GEO:cylinder[r=2,h=8][size:small]##
-$L = 2\text{ m}$ দীর্ঘ এবং $r = 4\text{ mm}$ ব্যাসার্ধবিশিষ্ট একটি ইস্পাত তারে $M = 15\text{ kg}$ ভর ঝুলালে তারটির দৈর্ঘ্য বৃদ্ধি কত হবে? ($Y = 2.0 \times 10^{11}\text{ N/m}^2, g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=1,h=4][size:small]##
+একটি $L = 2.0\text{ m}$ দীর্ঘ এবং $r = 1.0\text{ mm}$ ব্যাসার্ধের ইস্পাতের তারে $M = 10\text{ kg}$ ভর ঝুলিয়ে দেওয়া হলো। ইস্পাতের ইয়ং-এর গুণাঙ্ক $Y = 2.0 	imes 10^{11}\text{ N/m}^2$ হলে তারটির দৈর্ঘ্য বৃদ্ধি $\Delta L$ এবং তারের প্রতি একক আয়তনে সঞ্চিত স্থিতিশক্তি (Energy density) নির্ণয় কর ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=2,h=8][size:small]##</t>
+          <t>##GEO:cylinder[r=1,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 1)।</t>
+          <t>প্রস্থচ্ছেদ $A = \pi r^2 = \pi (10^{-3})^2 = \pi \times 10^{-6}\text{ m}^2$। বল $F = Mg = 10 \times 9.8 = 98\text{ N}$। পীড়ন $\sigma = \frac{F}{A} = \frac{98}{\pi\times 10^{-6}} \approx 3.119\times 10^7\text{ N/m}^2$। বিকৃতি $\epsilon = \frac{\sigma}{Y} = \frac{3.119\times 10^7}{2.0\times 10^{11}} \approx 1.56\times 10^{-4}$। দৈর্ঘ্য বৃদ্ধি $\Delta L = \epsilon L = 1.56\times 10^{-4} \times 2.0 = 3.12\times 10^{-4}\text{ m} = 0.312\text{ mm}$। শক্তি ঘনত্ব $u = \frac{1}{2}\sigma\epsilon = \frac{1}{2}(3.119\times 10^7)(1.56\times 10^{-4}) \approx 2432.6\text{ J/m}^3$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>দৈর্ঘ্য বৃদ্ধি $\Delta L = 3.12 \times 10^{-4}\text{ m} \approx 0.312\text{ mm}$, শক্তি ঘনত্ব $u = 2432.6\text{ J/m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3595,7 +3360,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>স্টোকসের সূত্র ও প্রান্তিক বেগ (সমস্যা 2)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3608,30 +3373,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: স্টোকসের সূত্র ও প্রান্তিক বেগ]
-##GEO:sphere[r=4][size:small]##
-$\rho = 7800\text{ kg/m}^3$ ঘনত্বের একটি ক্ষুদ্র লোহার গোলক $\sigma = 900\text{ kg/m}^3$ ঘনত্ব এবং $\eta = 0.8\text{ Pa}\cdot\text{s}$ সান্দ্রতা বিশিষ্ট তেলে ছেড়ে দেওয়া হলো। গোলকের ব্যাসার্ধ $r = 3\text{ mm}$ হলে প্রান্তিক বেগ ($v_t$) কত?</t>
+          <t>##GEO:cylinder[r=1.5,h=4.5][size:small]##
+একটি তারের উপাদানের পয়সনের অনুপাত $\sigma = 0.25$। তারটির ওপর অনুদৈর্ঘ্য বল প্রয়োগের ফলে এর দৈর্ঘ্য $0.1\%$ বৃদ্ধি পেল। তারটির ব্যাস শতকরা কত হ্রাস পাবে এবং তারটির আয়তনের শতকরা পরিবর্তন কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4.5][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 2)।</t>
+          <t>অনুদৈর্ঘ্য বিকৃতি $\frac{\Delta L}{L} = 0.1\% = 10^{-3}$। পয়সনের অনুপাত $\sigma = \frac{|\Delta r/r|}{\Delta L/L} \implies \frac{|\Delta r|}{r} = \sigma \frac{\Delta L}{L} = 0.25(0.1\%) = 0.025\%$ (হ্রাস)। তারের আয়তন $V = \pi r^2 L \implies \frac{\Delta V}{V} = \frac{\Delta L}{L} - 2\frac{|\Delta r|}{r} = \frac{\Delta L}{L}(1 - 2\sigma) = 0.1\%(1 - 2(0.25)) = 0.1\%(0.5) = +0.05\%$ (আয়তন বৃদ্ধি পায়)।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>ব্যাস হ্রাস পাবে $0.025\%$, আয়তন বৃদ্ধি পাবে $0.05\%$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3651,38 +3411,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান (সমস্যা 3)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান]
-$r = 0.4\text{ mm}$ ব্যাসার্ধের একটি কৈশিক নলকে পানিতে খাড়াভাবে ডুবালে পানি নলের ভেতর $h = 8\text{ cm}$ ওপরে ওঠে। পানির পৃষ্ঠটান $T$ নির্ণয় কর। (পানির ঘনত্ব $\rho = 1000\text{ kg/m}^3, g = 9.8\text{ m/s}^2$, স্পর্শ কোণ $\theta = 0^\circ$)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি তামার তারের দুই প্রান্ত দুটি দৃঢ় ভিত্তির সাথে এমনভাবে দৃঢ়ভাবে বাঁধা আছে যে $30^\circ\text{C}$ তাপমাত্রায় তারে কোনো টান নেই। তাপমাত্রা কমে $10^\circ\text{C}$ হলে তারটিতে উৎপন্ন তাপীয় পীড়ন (Thermal stress) এবং টান বলের মান কত? (তারের ব্যাস $2\text{ mm}, Y = 1.2 	imes 10^{11}\text{ N/m}^2, \alpha = 1.7 	imes 10^{-5}\text{ K}^{-1}$)।</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 3)।</t>
+          <t>তাপমাত্রা হ্রাস $\Delta\theta = 30 - 10 = 20\text{ K}$। তাপীয় পীড়ন $\sigma = Y \alpha \Delta\theta = (1.2\times 10^{11})(1.7\times 10^{-5})(20) = 4.08\times 10^7\text{ N/m}^2$। প্রস্থচ্ছেদ $A = \frac{\pi}{4}(2\times 10^{-3})^2 = \pi\times 10^{-6}\text{ m}^2$। টান বল $F = \sigma A = (4.08\times 10^7)(\pi\times 10^{-6}) = 40.8\pi \approx 128.18\text{ N}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>তাপীয় পীড়ন $\sigma = 4.08 \times 10^7\text{ N/m}^2$, টান বল $F = 128.18\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3702,7 +3462,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>সাবান বুদবুদের অতিরিক্ত চাপ (সমস্যা 4)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3715,25 +3475,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: সাবান বুদবুদের অতিরিক্ত চাপ]
-বাতাসে $R = 5\text{ cm}$ ব্যাসার্ধের একটি সাবানের বুদবুদ তৈরি করা হলো। সাবান পানির পৃষ্ঠটান $T = 0.03\text{ N/m}$ হলে বুদবুদের ভেতরের অতিরিক্ত চাপ $\Delta P = \frac{4T}{R}$ কত প্যাস্কেল?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##
+একটি তারের দৈর্ঘ্য টেনে দ্বিগুণ করা হলো। যদি হুকের সূত্র এই চরম সীমা পর্যন্ত প্রযোজ্য থাকে, তবে তারটিতে অনুদৈর্ঘ্য বিকৃতি এবং অসহ পীড়ন ইয়ং-এর গুণাঙ্কের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 4)।</t>
+          <t>আদি দৈর্ঘ্য $L$, শেষ দৈর্ঘ্য $2L$। দৈর্ঘ্য বৃদ্ধি $\Delta L = 2L - L = L$। অনুদৈর্ঘ্য বিকৃতি $\epsilon = \frac{\Delta L}{L} = \frac{L}{L} = 1.0$ ($100\%$ বিকৃতি)। হুকের সূত্র অনুসারে পীড়ন $\sigma = Y \epsilon = Y(1.0) = Y$ (অর্থাৎ ইয়ং-এর গুণাঙ্ক হলো এমন তাত্ত্বিক পীড়ন যা কোনো তারের দৈর্ঘ্য দ্বিগুণ করতে প্রয়োজন)।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>বিকৃতি $\epsilon = 1.0$, পীড়ন $\sigma = Y$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3753,38 +3513,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>আয়তন গুণাঙ্ক ও সংনম্যতা (সমস্যা 5)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: আয়তন গুণাঙ্ক ও সংনম্যতা]
-একটি তরলের ওপর চাপ $\Delta P = 6 \times 10^6\text{ Pa}$ বৃদ্ধি করায় এর আয়তন $0.2\%$ হ্রাস পায়। তরলটির আয়তন গুণাঙ্ক ($K$) এবং সংনম্যতা ($k = 1/K$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি রাবার কর্ডের ব্যাস $8\text{ mm}$ এবং দৈর্ঘ্য $1.0\text{ m}$। এতে $5\text{ kg}$ ভর চাপালে দৈর্ঘ্য $10\text{ cm}$ প্রসারিত হয়। রাবারের ইয়ং-এর গুণাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 5)।</t>
+          <t>$F = 5 \times 9.8 = 49\text{ N}$। ব্যাসার্ধ $r = 4\text{ mm} = 4\times 10^{-3}\text{ m}$। $A = \pi (4\times 10^{-3})^2 = 16\pi\times 10^{-6}\text{ m}^2 \approx 5.027\times 10^{-5}\text{ m}^2$। প্রসারণ $\Delta L = 0.10\text{ m}$। $Y = \frac{F L}{A \Delta L} = \frac{49 \times 1.0}{(5.027\times 10^{-5})(0.10)} = \frac{49}{5.027\times 10^{-6}} \approx 9.75\times 10^5\text{ N/m}^2$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>$Y = 9.75 \times 10^5\text{ N/m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3804,7 +3564,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক (সমস্যা 6)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3817,25 +3577,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক]
-$L = 1.0\text{ m}$ দৈর্ঘ্য এবং $r = 1\text{ cm}$ ব্যাসার্ধের একটি নিরেট ধাতব দণ্ডের এক প্রান্ত দৃঢ়ভাবে আটকে অপর প্রান্তে $\theta = 4^\circ$ মোচড় দিতে কত টর্কের প্রয়োজন হবে? (দৃঢ়তার গুণাঙ্ক $\eta = 4 \times 10^{10}\text{ N/m}^2$)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+পানির আয়তন গুণাঙ্ক (Bulk Modulus) $B = 2.0 	imes 10^9\text{ N/m}^2$। সমুদ্রের কত গভীরে গেলে পানির ঘনত্ব ভূপৃষ্ঠের ঘনত্বের চেয়ে $0.5\%$ বৃদ্ধি পাবে? (পানির গড় ঘনত্ব $\rho = 1000\text{ kg/m}^3, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 6)।</t>
+          <t>ঘনত্ব বৃদ্ধি $\frac{\Delta\rho}{\rho} = -\frac{\Delta V}{V} = 0.005$। বাল্ক মডুলাস $B = \frac{\Delta P}{|\Delta V/V|} \implies \Delta P = B\left(\frac{\Delta\rho}{\rho}\right) = (2.0\times 10^9)(0.005) = 1.0\times 10^7\text{ N/m}^2$। সমুদ্রের চাপ $\Delta P = \rho g h \implies h = \frac{\Delta P}{\rho g} = \frac{10^7}{1000 \times 9.8} \approx 1020.4\text{ m}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>গভীরতা $h = 1020.4\text{ m} \approx 1.02\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3855,38 +3615,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>তারের একক আয়তনে সঞ্চিত শক্তি (সমস্যা 7)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: তারের একক আয়তনে সঞ্চিত শক্তি]
-$Y = 2.0 \times 10^{11}\text{ N/m}^2$ বিশিষ্ট একটি তারে টান প্রয়োগ করে $0.2\%$ অনুদৈর্ঘ্য বিকৃতি ঘটানো হলো। তারটির প্রতি ঘনমিটার আয়তনে সঞ্চিত স্থিতিস্থাপক স্থিতিশক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##
+সমান দৈর্ঘ্য $L$ এবং সমান ব্যাস বিশিষ্ট একটি তামা ও একটি লোহার তারকে জোড়া লাগিয়ে মোট দৈর্ঘ্য $2L$ করা হলো। জোড়া তারটির একপ্রান্তে বল $F$ প্রয়োগ করলে তাদের মোট দৈর্ঘ্য বৃদ্ধি $\Delta L$ হয়। জোড়া তারটির তুল্য ইয়ং-এর গুণাঙ্ক $Y_{eq}$ নির্ণয় কর ($Y_{Fe} = 2.0 	imes 10^{11}\text{ N/m}^2, Y_{Cu} = 1.0 	imes 10^{11}\text{ N/m}^2$)।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 7)।</t>
+          <t>শ্রেণি সমবায়ে উভয় তারে টান বল $F$ সমান। মোট বৃদ্ধি $\Delta L = \Delta L_1 + \Delta L_2 = \frac{FL}{A Y_1} + \frac{FL}{A Y_2} = \frac{FL}{A}\left(\frac{1}{Y_1} + \frac{1}{Y_2}\right)$। তুল্য তারের জন্য: $\Delta L = \frac{F(2L)}{A Y_{eq}}$। সমীকৃত করে: $\frac{2}{Y_{eq}} = \frac{1}{Y_1} + \frac{1}{Y_2} \implies Y_{eq} = \frac{2 Y_1 Y_2}{Y_1 + Y_2} = \frac{2(2.0\times 10^{11})(1.0\times 10^{11})}{3.0\times 10^{11}} = 1.33\times 10^{11}\text{ N/m}^2$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$Y_{eq} = \frac{2 Y_1 Y_2}{Y_1 + Y_2} = 1.33 \times 10^{11}\text{ N/m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3906,7 +3666,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ (সমস্যা 8)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3919,25 +3679,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ]
-একটি অনুভূমিক নলে পানি প্রবাহিত হচ্ছে। নলের যে অংশের প্রস্থচ্ছেদ $A_1 = 3\text{ cm}^2$, সেখানে বেগ $v_1 = 2\text{ m/s}$ এবং চাপ $P_1 = 1.5 \times 10^5\text{ Pa}$। অন্য প্রান্তে যেখানে $A_2 = 8\text{ cm}^2$, সেখানে পানির বেগ ও চাপ কত?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:cylinder[r=0.8,h=5][size:small]##
+একটি তারের উপাদানকে টেনে তারের ব্যাসার্ধ অর্ধেক ($r' = r/2$) করা হলো। এর ফলে তারটির দৈর্ঘ্য কত গুণ বৃদ্ধি পাবে এবং একই ভারের জন্য নতুন তারের দৈর্ঘ্য বৃদ্ধি আগের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=0.8,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 8)।</t>
+          <t>উপাদানের আয়তন ধ্রুব: $V = \pi r^2 L = \pi (r/2)^2 L' \implies \pi r^2 L = \frac{\pi r^2}{4} L' \implies L' = 4L$ (দৈর্ঘ্য ৪ গুণ হয়)। দৈর্ঘ্য বৃদ্ধি $\Delta L = \frac{FL}{A Y} = \frac{FL}{\pi r^2 Y}$। নতুন তারে: $\Delta L' = \frac{F(4L)}{\pi(r/2)^2 Y} = \frac{4FL}{\frac{\pi r^2}{4}Y} = 16 \frac{FL}{\pi r^2 Y} = 16 \Delta L$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>দৈর্ঘ্য ৪ গুণ বৃদ্ধি পাবে, দৈর্ঘ্য বৃদ্ধি আগের ১৬ গুণ হবে</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3957,38 +3717,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>টরেসেলির উপপাদ্য ও নির্গমন বেগ (সমস্যা 9)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: টরেসেলির উপপাদ্য ও নির্গমন বেগ]
-একটি পানির ট্যাংকের তলদেশ থেকে $h = 4\text{ m}$ নিচে একটি ক্ষুদ্র ছিদ্র রয়েছে। ছিদ্র দিয়ে পানি নির্গমনের বেগ ($v = \sqrt{2gh}$) এবং প্রতি সেকেন্ডে নির্গত পানির আয়তন কত? (ছিদ্রের ক্ষেত্রফল $A = 1\text{ cm}^2$)</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.2,h=4][size:small]##
+একটি ধাতব তারের দৈর্ঘ্য $3\text{ m}$ এবং প্রস্থচ্ছেদের ক্ষেত্রফল $2\text{ mm}^2$। তারটিতে $500\text{ N}$ বল প্রয়োগ করে প্রসারিত করা হলো। তারের উপাদানের ইয়ং-এর গুণাঙ্ক $Y = 1.5 	imes 10^{11}\text{ N/m}^2$ হলে তারটিতে সঞ্চিত মোট স্থিতিশক্তি কত জুল?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 9)।</t>
+          <t>পীড়ন $\sigma = \frac{500}{2\times 10^{-6}} = 2.5\times 10^8\text{ N/m}^2$। বিকৃতি $\epsilon = \frac{\sigma}{Y} = \frac{2.5\times 10^8}{1.5\times 10^{11}} = \frac{5}{3}\times 10^{-3}$। তারের মোট আয়তন $V = A L = (2\times 10^{-6}\text{ m}^2)(3\text{ m}) = 6\times 10^{-6}\text{ m}^3$। মোট শক্তি $U = \frac{1}{2}\sigma\epsilon V = \frac{1}{2}(2.5\times 10^8)\left(\frac{5}{3}\times 10^{-3}\right)(6\times 10^{-6}) = 1.25\text{ J}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>মোট সঞ্চিত শক্তি $U = 1.25\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4008,7 +3768,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>পয়সনের অনুপাত ও ব্যাস হ্রাস (সমস্যা 10)</t>
+          <t>স্থিতিস্থাপকতা, পীড়ন-বিকৃতি ও স্থিতিশক্তি (Elasticity &amp; Moduli)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4021,25 +3781,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: পয়সনের অনুপাত ও ব্যাস হ্রাস]
-একটি তারের ওপর টান বল প্রয়োগ করায় এর দৈর্ঘ্য বিকৃতি $0.5\%$ ঘটে। উপাদানটির পয়সনের অনুপাত $\sigma = 0.2$ হলে তারটির ব্যাস শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:cube[s=3][size:small]##
+একটি খাঁটি পদার্থের ক্ষেত্রে স্থিতিস্থাপক গুণাঙ্কসমূহ $Y$, $K$ (বাল্ক মডুলাস) এবং $\eta$ (দৃঢ়তা গুণাঙ্ক)-এর মধ্যকার তাত্ত্বিক সম্পর্ক $\frac{9}{Y} = \frac{1}{K} + \frac{3}{\eta}$। কোনো পদার্থের $K = 1.4 	imes 10^{11}\text{ N/m}^2$ এবং $\eta = 0.6 	imes 10^{11}\text{ N/m}^2$ হলে ইয়ং-এর গুণাঙ্ক $Y$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:cube[s=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 10)।</t>
+          <t>$\frac{9}{Y} = \frac{1}{1.4\times 10^{11}} + \frac{3}{0.6\times 10^{11}} = \frac{1}{1.4\times 10^{11}} + \frac{5}{1.0\times 10^{11}} = (0.714 + 5.0)\times 10^{-11} = 5.714\times 10^{-11}$। $Y = \frac{9}{5.714\times 10^{-11}} \approx 1.575\times 10^{11}\text{ N/m}^2$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>$Y = 1.57 \times 10^{11}\text{ N/m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4059,43 +3819,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ (সমস্যা 11)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[সমস্যা 11: ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ]
-##GEO:cylinder[r=2,h=8][size:small]##
-$L = 6\text{ m}$ দীর্ঘ এবং $r = 4\text{ mm}$ ব্যাসার্ধবিশিষ্ট একটি ইস্পাত তারে $M = 30\text{ kg}$ ভর ঝুলালে তারটির দৈর্ঘ্য বৃদ্ধি কত হবে? ($Y = 2.0 \times 10^{11}\text{ N/m}^2, g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+পানির পৃষ্ঠটান $T = 7.2 	imes 10^{-2}\text{ N/m}$। $r = 1.0\text{ mm}$ ব্যাসার্ধের একটি কাচ কৈশিক নল বিশুদ্ধ পানিতে খাড়াভাবে নিমজ্জিত করলে নলে পানি কত উচ্চতায় উঠবে? (স্পর্শ কোণ $\theta = 0^\circ, \rho = 1000\text{ kg/m}^3, g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=2,h=8][size:small]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 11)।</t>
+          <t>কৈশিক উত্থানের সূত্র: $h = \frac{2T\cos\theta}{r\rho g}$। মান বসিয়ে: $h = \frac{2(7.2\times 10^{-2})\cos 0^\circ}{(1.0\times 10^{-3})(1000)(9.8)} = \frac{0.144}{9.8} \approx 0.01469\text{ m} = 1.47\text{ cm}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>উচ্চতা $h = 1.47\text{ cm} = 1.47 \times 10^{-2}\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4115,7 +3870,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>স্টোকসের সূত্র ও প্রান্তিক বেগ (সমস্যা 12)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4128,30 +3883,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: স্টোকসের সূত্র ও প্রান্তিক বেগ]
-##GEO:sphere[r=4][size:small]##
-$\rho = 7800\text{ kg/m}^3$ ঘনত্বের একটি ক্ষুদ্র লোহার গোলক $\sigma = 900\text{ kg/m}^3$ ঘনত্ব এবং $\eta = 0.8\text{ Pa}\cdot\text{s}$ সান্দ্রতা বিশিষ্ট তেলে ছেড়ে দেওয়া হলো। গোলকের ব্যাসার্ধ $r = 1\text{ mm}$ হলে প্রান্তিক বেগ ($v_t$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+সাবান পানির পৃষ্ঠটান $T = 3.0 	imes 10^{-2}\text{ N/m}$। $R = 2.0\text{ cm}$ ব্যাসার্ধের একটি সাবানের বুদবুদ ফুঁ দিয়ে তৈরি করতে কত জুল কাজ সম্পন্ন করতে হবে?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 12)।</t>
+          <t>সাবানের বুদবুদের দুটি মুক্ত তল (ভেতরে ও বাইরে) থাকে: ক্ষেত্রফল $A = 2 \times (4\pi R^2) = 8\pi R^2$। কৃতকাজ $W = T \Delta A = T(8\pi R^2) = (3.0\times 10^{-2}) \times 8\pi (0.02)^2 = 0.24\pi \times 0.0004 = 9.6\pi \times 10^{-5} \approx 3.016\times 10^{-4}\text{ J}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>কৃতকাজ $W = 3.02 \times 10^{-4}\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4171,38 +3921,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান (সমস্যা 13)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান]
-$r = 0.2\text{ mm}$ ব্যাসার্ধের একটি কৈশিক নলকে পানিতে খাড়াভাবে ডুবালে পানি নলের ভেতর $h = 8\text{ cm}$ ওপরে ওঠে। পানির পৃষ্ঠটান $T$ নির্ণয় কর। (পানির ঘনত্ব $\rho = 1000\text{ kg/m}^3, g = 9.8\text{ m/s}^2$, স্পর্শ কোণ $\theta = 0^\circ$)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি সাবানের বুদবুদের ব্যাসার্ধ $r = 1.0\text{ cm}$ এবং পানির ফোঁটার ব্যাসার্ধ $r = 1.0\text{ mm}$। উভয়ের অভ্যন্তরে অতিরিক্ত চাপ (Excess pressure) কত? (সাবান পানির $T_1 = 0.03\text{ N/m}$, বিশুদ্ধ পানির $T_2 = 0.072\text{ N/m}$)।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 13)।</t>
+          <t>সাবানের বুদবুদে দুটি তল: $\Delta P_1 = \frac{4T_1}{r_1} = \frac{4(0.03)}{0.01} = \frac{0.12}{0.01} = 12.0\text{ Pa}$। পানির ফোঁটায় একটি তল: $\Delta P_2 = \frac{2T_2}{r_2} = \frac{2(0.072)}{10^{-3}} = \frac{0.144}{10^{-3}} = 144.0\text{ Pa}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>বুদবুদে অতিরিক্ত চাপ $\Delta P_1 = 12.0\text{ Pa}$, ফোঁটায় অতিরিক্ত চাপ $\Delta P_2 = 144.0\text{ Pa}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4222,7 +3972,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>সাবান বুদবুদের অতিরিক্ত চাপ (সমস্যা 14)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4235,25 +3985,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: সাবান বুদবুদের অতিরিক্ত চাপ]
-বাতাসে $R = 3\text{ cm}$ ব্যাসার্ধের একটি সাবানের বুদবুদ তৈরি করা হলো। সাবান পানির পৃষ্ঠটান $T = 0.03\text{ N/m}$ হলে বুদবুদের ভেতরের অতিরিক্ত চাপ $\Delta P = \frac{4T}{R}$ কত প্যাস্কেল?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একই আকারের $1000$ টি ক্ষুদ্র পারদ ফোঁটা একত্রিত হয়ে একটি বৃহৎ পারদ ফোঁটায় পরিণত হলো। পৃষ্ঠটানের কারণে মুক্ত শক্তির পরিমাণ নির্ণয় কর। (প্রতিটি ক্ষুদ্র ফোঁটার ব্যাসার্ধ $r = 1.0\text{ mm}$, পারদের পৃষ্ঠটান $T = 0.465\text{ N/m}$)।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 14)।</t>
+          <t>আয়তন ধ্রুব: $\frac{4}{3}\pi R^3 = 1000\left(\frac{4}{3}\pi r^3\right) \implies R = 10 r = 10(1\text{ mm}) = 10\text{ mm} = 0.01\text{ m}$। প্রারম্ভিক ক্ষেত্রফল $A_1 = 1000(4\pi r^2) = 4000\pi r^2$। শেষ ক্ষেত্রফল $A_2 = 4\pi R^2 = 4\pi(100r^2) = 400\pi r^2$। ক্ষেত্রফল হ্রাস $\Delta A = 3600\pi r^2 = 3600\pi(10^{-3})^2 = 3.6\pi\times 10^{-3}\text{ m}^2$। মুক্ত শক্তি $\Delta E = T \Delta A = 0.465 \times 3.6\pi\times 10^{-3} \approx 5.26\times 10^{-3}\text{ J}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>মুক্ত শক্তি $\Delta E = 5.26 \times 10^{-3}\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4273,38 +4023,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>আয়তন গুণাঙ্ক ও সংনম্যতা (সমস্যা 15)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: আয়তন গুণাঙ্ক ও সংনম্যতা]
-একটি তরলের ওপর চাপ $\Delta P = 4 \times 10^6\text{ Pa}$ বৃদ্ধি করায় এর আয়তন $0.2\%$ হ্রাস পায়। তরলটির আয়তন গুণাঙ্ক ($K$) এবং সংনম্যতা ($k = 1/K$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+কাচ ও পারদের স্পর্শ কোণ $\theta = 135^\circ$। $r = 0.5\text{ mm}$ ব্যাসার্ধের একটি কাচ কৈশিক নল পারদে নিমজ্জিত করলে নলের ভেতর পারদের তল বাইরে অপেক্ষা কত নিচে নেমে যাবে? (পারদের ঘনত্ব $\rho = 13600\text{ kg/m}^3, T = 0.48\text{ N/m}, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 15)।</t>
+          <t>$h = \frac{2T\cos\theta}{r\rho g}$। $\cos 135^\circ = -\frac{1}{\sqrt{2}} \approx -0.7071$। $h = \frac{2(0.48)(-0.7071)}{(0.5\times 10^{-3})(13600)(9.8)} = \frac{-0.6788}{66.64} \approx -0.01019\text{ m} = -1.02\text{ cm}$ (ঋণাত্মক চিহ্ন নির্দেশ করে পারদ তল ১.০২ সেমি নিচে নেমে যাবে)।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>পারদ স্তম্ভ অবনমন $h = 1.02\text{ cm} = 1.02 \times 10^{-2}\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4324,7 +4074,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক (সমস্যা 16)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4337,25 +4087,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক]
-$L = 1.0\text{ m}$ দৈর্ঘ্য এবং $r = 5\text{ cm}$ ব্যাসার্ধের একটি নিরেট ধাতব দণ্ডের এক প্রান্ত দৃঢ়ভাবে আটকে অপর প্রান্তে $\theta = 4^\circ$ মোচড় দিতে কত টর্কের প্রয়োজন হবে? (দৃঢ়তার গুণাঙ্ক $\eta = 4 \times 10^{10}\text{ N/m}^2$)</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সাবানের বুদবুদের ব্যাস $2\text{ cm}$ হতে ফুঁ দিয়ে বৃদ্ধি করে $4\text{ cm}$ করা হলো। পৃষ্ঠটান $T = 0.03\text{ N/m}$ হলে সম্পাদিত কাজের পরিমাণ কত?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 16)।</t>
+          <t>$R_1 = 0.01\text{ m}, R_2 = 0.02\text{ m}$। ক্ষেত্রফলের বৃদ্ধি (দুটি তলের জন্য): $\Delta A = 2 \times 4\pi (R_2^2 - R_1^2) = 8\pi (0.0004 - 0.0001) = 8\pi(0.0003) = 2.4\pi\times 10^{-3}\text{ m}^2$। কৃতকাজ $W = T \Delta A = 0.03 \times 2.4\pi\times 10^{-3} = 7.2\pi\times 10^{-5} \approx 2.262\times 10^{-4}\text{ J}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>কৃতকাজ $W = 2.26 \times 10^{-4}\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4375,38 +4125,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>তারের একক আয়তনে সঞ্চিত শক্তি (সমস্যা 17)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: তারের একক আয়তনে সঞ্চিত শক্তি]
-$Y = 2.0 \times 10^{11}\text{ N/m}^2$ বিশিষ্ট একটি তারে টান প্রয়োগ করে $0.6\%$ অনুদৈর্ঘ্য বিকৃতি ঘটানো হলো। তারটির প্রতি ঘনমিটার আয়তনে সঞ্চিত স্থিতিস্থাপক স্থিতিশক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+দুটি সাবানের বুদবুদের ব্যাসার্ধ যথাক্রমে $r_1 = 3\text{ cm}$ এবং $r_2 = 4\text{ cm}$। এদের একত্রীকরণে সৃষ্ট সাধারণ ঝিল্লির (Common interface) বক্রতার ব্যাসার্ধ $R$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 17)।</t>
+          <t>চাপের পার্থক্য: $\Delta P_1 - \Delta P_2 = \Delta P \implies \frac{4T}{r_1} - \frac{4T}{r_2} = \frac{4T}{R} \implies \frac{1}{R} = \frac{1}{r_1} - \frac{1}{r_2} = \frac{1}{3} - \frac{1}{4} = \frac{1}{12} \implies R = 12.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>বক্রতার ব্যাসার্ধ $R = 12.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4426,7 +4176,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ (সমস্যা 18)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4439,25 +4189,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ]
-একটি অনুভূমিক নলে পানি প্রবাহিত হচ্ছে। নলের যে অংশের প্রস্থচ্ছেদ $A_1 = 1\text{ cm}^2$, সেখানে বেগ $v_1 = 2\text{ m/s}$ এবং চাপ $P_1 = 1.5 \times 10^5\text{ Pa}$। অন্য প্রান্তে যেখানে $A_2 = 8\text{ cm}^2$, সেখানে পানির বেগ ও চাপ কত?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=1.8][size:small]##
+বায়ুমণ্ডলে ভেসে থাকা দুটি পানির ফোঁটার ব্যাসার্ধের অনুপাত $1:2$ হলে তাদের অভ্যন্তরের অতিরিক্ত চাপের অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=1.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 18)।</t>
+          <t>পানির ফোঁটার অতিরিক্ত চাপ $\Delta P = \frac{2T}{r} \propto \frac{1}{r}$। অনুপাত $\frac{\Delta P_1}{\Delta P_2} = \frac{r_2}{r_1} = \frac{2}{1} = 2:1$ (ক্ষুদ্রতর ফোঁটায় অভ্যন্তরীণ চাপ দ্বিগুণ বেশি থাকে)।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$\Delta P_1 : \Delta P_2 = 2 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4477,38 +4227,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>টরেসেলির উপপাদ্য ও নির্গমন বেগ (সমস্যা 19)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: টরেসেলির উপপাদ্য ও নির্গমন বেগ]
-একটি পানির ট্যাংকের তলদেশ থেকে $h = 2\text{ m}$ নিচে একটি ক্ষুদ্র ছিদ্র রয়েছে। ছিদ্র দিয়ে পানি নির্গমনের বেগ ($v = \sqrt{2gh}$) এবং প্রতি সেকেন্ডে নির্গত পানির আয়তন কত? (ছিদ্রের ক্ষেত্রফল $A = 1\text{ cm}^2$)</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=2,b=3.46,angle=30][size:small]##
+একটি উলম্ব কৈশিক নলে পানি $h$ উচ্চতায় ওঠে। নলটিকে উল্লম্বের সাথে $60^\circ$ কোণে হেলিয়ে দিলে নলের অক্ষ বরাবর পানির দৈর্ঘ্য $l$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=2,b=3.46,angle=30][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 19)।</t>
+          <t>কৈশিক ক্রিয়ায় উল্লম্ব উচ্চতা $h$ সর্বদা ধ্রুব থাকে। হেলানো নলে উল্লম্ব উচ্চতা $h = l\cos\theta \implies l = \frac{h}{\cos 60^\circ} = \frac{h}{0.5} = 2h$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>নল বরাবর দৈর্ঘ্য $l = 2h$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4528,7 +4278,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>পয়সনের অনুপাত ও ব্যাস হ্রাস (সমস্যা 20)</t>
+          <t>পৃষ্ঠটান, অতিরিক্ত চাপ ও কৈশিক নল (Surface Tension &amp; Capillarity)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4541,25 +4291,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: পয়সনের অনুপাত ও ব্যাস হ্রাস]
-একটি তারের ওপর টান বল প্রয়োগ করায় এর দৈর্ঘ্য বিকৃতি $0.3\%$ ঘটে। উপাদানটির পয়সনের অনুপাত $\sigma = 0.2$ হলে তারটির ব্যাস শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+পানির নিচে $h = 10\text{ m}$ গভীরতায় একটি বায়ুর বুদবুদ সৃষ্টি হলো। বুদবুদটির ব্যাসার্ধ $r = 0.1\text{ mm}$। বায়ুমণ্ডলীয় চাপ $1.013 	imes 10^5\text{ N/m}^2$ এবং পৃষ্ঠটান $0.073\text{ N/m}$ হলে বুদবুদের অভ্যন্তরে মোট পরম চাপ কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 20)।</t>
+          <t>পানির বাইরে চাপ $P_{water} = P_{atm} + \rho g h = 1.013\times 10^5 + 1000(9.8)(10) = 1.013\times 10^5 + 9.8\times 10^4 = 1.993\times 10^5\text{ Pa}$। বুদবুদের অতিরিক্ত চাপ $\Delta P = \frac{2T}{r} = \frac{2(0.073)}{10^{-4}} = 1460\text{ Pa} = 0.0146\times 10^5\text{ Pa}$। মোট পরম চাপ $P_{in} = P_{water} + \Delta P = 1.993\times 10^5 + 0.0146\times 10^5 \approx 2.0076\times 10^5\text{ Pa}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>মোট চাপ $P_{in} = 2.0076 \times 10^5\text{ Pa}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4579,43 +4329,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ (সমস্যা 21)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[সমস্যা 21: ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ]
-##GEO:cylinder[r=2,h=8][size:small]##
-$L = 4\text{ m}$ দীর্ঘ এবং $r = 4\text{ mm}$ ব্যাসার্ধবিশিষ্ট একটি ইস্পাত তারে $M = 10\text{ kg}$ ভর ঝুলালে তারটির দৈর্ঘ্য বৃদ্ধি কত হবে? ($Y = 2.0 \times 10^{11}\text{ N/m}^2, g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:circle[r=2][size:small]##
+গ্লিসারিনের ঘনত্ব $\sigma = 1.26 	imes 10^3\text{ kg/m}^3$ এবং সান্দ্রতা গুণাঙ্ক $\eta = 0.83\text{ Pa}\cdot\text{s}$। এতে $r = 2.0\text{ mm}$ ব্যাসার্ধের একটি ইস্পাতের বল ($+ho = 7.8 	imes 10^3\text{ kg/m}^3$) ছেড়ে দিলে বলটির প্রান্তীয় বেগ (Terminal velocity) কত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=2,h=8][size:small]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 21)।</t>
+          <t>স্টোকসের সূত্র হতে প্রান্তীয় বেগ: $v_t = \frac{2r^2(\rho - \sigma)g}{9\eta}$। মান বসিয়ে: $v_t = \frac{2(2\times 10^{-3})^2(7800 - 1260)(9.8)}{9(0.83)} = \frac{2(4\times 10^{-6})(6540)(9.8)}{7.47} = \frac{0.5127}{7.47} \approx 0.0686\text{ m/s} \approx 6.9\text{ cm/s}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>প্রান্তীয় বেগ $v_t = 0.069\text{ m/s} = 6.9\text{ cm/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4635,7 +4381,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>স্টোকসের সূত্র ও প্রান্তিক বেগ (সমস্যা 22)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4648,30 +4394,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: স্টোকসের সূত্র ও প্রান্তিক বেগ]
-##GEO:sphere[r=4][size:small]##
-$\rho = 7800\text{ kg/m}^3$ ঘনত্বের একটি ক্ষুদ্র লোহার গোলক $\sigma = 900\text{ kg/m}^3$ ঘনত্ব এবং $\eta = 0.8\text{ Pa}\cdot\text{s}$ সান্দ্রতা বিশিষ্ট তেলে ছেড়ে দেওয়া হলো। গোলকের ব্যাসার্ধ $r = 5\text{ mm}$ হলে প্রান্তিক বেগ ($v_t$) কত?</t>
+          <t>##GEO:circle[r=1.5][size:small]##
+বাতাসে পতনশীল একটি বৃষ্টির ফোঁটার প্রান্তিক বেগ $v_t = 9.0\text{ m/s}$। বাতাসের সান্দ্রতা $\eta = 1.8 	imes 10^{-5}\text{ Pa}\cdot\text{s}$ এবং পানির ঘনত্ব $\rho = 1000\text{ kg/m}^3$ হলে ফোঁটাটির ব্যাসার্ধ নির্ণয় কর (বাতাসের ঘনত্ব অগ্রাহ্য করে, $g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=1.5][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 22)।</t>
+          <t>$v_t = \frac{2 r^2 \rho g}{9\eta} \implies r^2 = \frac{9\eta v_t}{2\rho g} = \frac{9(1.8\times 10^{-5})(9.0)}{2(1000)(9.8)} = \frac{1.458\times 10^{-3}}{19600} \approx 7.439\times 10^{-8}\text{ m}^2$। $r = \sqrt{7.439\times 10^{-8}} \approx 2.73\times 10^{-4}\text{ m} \approx 0.27\text{ mm}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>ব্যাসার্ধ $r = 0.288\text{ mm} = 2.88 \times 10^{-4}\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4691,38 +4432,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান (সমস্যা 23)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান]
-$r = 0.6\text{ mm}$ ব্যাসার্ধের একটি কৈশিক নলকে পানিতে খাড়াভাবে ডুবালে পানি নলের ভেতর $h = 8\text{ cm}$ ওপরে ওঠে। পানির পৃষ্ঠটান $T$ নির্ণয় কর। (পানির ঘনত্ব $\rho = 1000\text{ kg/m}^3, g = 9.8\text{ m/s}^2$, স্পর্শ কোণ $\theta = 0^\circ$)</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+সমান আকারের দুটি বৃষ্টির ফোঁটা বাতাসে একই প্রান্তিক বেগ $v = 5\text{ cm/s}$ নিয়ে পড়ছিল। ফোঁটা দুটি একত্রিত হয়ে একটি একক ফোঁটা গঠন করলে নতুন ফোঁটাটির প্রান্তিক বেগ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 23)।</t>
+          <t>আয়তন সংরক্ষণ: $\frac{4}{3}\pi R^3 = 2\left(\frac{4}{3}\pi r^3\right) \implies R = 2^{1/3} r$। প্রান্তিক বেগ $v \propto r^2$। নতুন বেগ $v' = v\left(\frac{R}{r}\right)^2 = v (2^{1/3})^2 = v 2^{2/3} = 5 \times 2^{2/3} \approx 5 \times 1.5874 \approx 7.94\text{ cm/s}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>নতুন প্রান্তীয় বেগ $v' = 7.94\text{ cm/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4742,7 +4483,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>সাবান বুদবুদের অতিরিক্ত চাপ (সমস্যা 24)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4755,25 +4496,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: সাবান বুদবুদের অতিরিক্ত চাপ]
-বাতাসে $R = 1\text{ cm}$ ব্যাসার্ধের একটি সাবানের বুদবুদ তৈরি করা হলো। সাবান পানির পৃষ্ঠটান $T = 0.03\text{ N/m}$ হলে বুদবুদের ভেতরের অতিরিক্ত চাপ $\Delta P = \frac{4T}{R}$ কত প্যাস্কেল?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+পয়েসিলির সমীকরণ (Poiseuille's equation) অনুসারে অনুভূমিক নলের মধ্য দিয়ে তরল প্রবাহের হার $Q = \frac{\pi P r^4}{8\eta L}$। একটি নলের ব্যাসার্ধ $10\%$ হ্রাস পেলে একই চাপে তরল প্রবাহের হার শতকরা কত হ্রাস পাবে?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 24)।</t>
+          <t>নতুন ব্যাসার্ধ $r' = 0.9r$। প্রবাহের হার $Q \propto r^4$। নতুন প্রবাহ $Q' \propto (0.9r)^4 = 0.6561 r^4 = 0.6561 Q$। প্রবাহ হ্রাসের শতকরা হার $= (1 - 0.6561) \times 100\% = 34.39\%$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>প্রবাহের হার $34.39\%$ হ্রাস পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4793,38 +4534,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>আয়তন গুণাঙ্ক ও সংনম্যতা (সমস্যা 25)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: আয়তন গুণাঙ্ক ও সংনম্যতা]
-একটি তরলের ওপর চাপ $\Delta P = 2 \times 10^6\text{ Pa}$ বৃদ্ধি করায় এর আয়তন $0.2\%$ হ্রাস পায়। তরলটির আয়তন গুণাঙ্ক ($K$) এবং সংনম্যতা ($k = 1/K$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি ধাতব প্লেটের ক্ষেত্রফল $A = 0.1\text{ m}^2$। প্লেটটি একটি তরল স্তরের ওপর অনুভূমিকভাবে $v = 0.5\text{ m/s}$ সমবেগে টানা হচ্ছে। তরল স্তরের পুরুত্ব $d = 2\text{ mm}$ এবং প্রয়োজনীয় স্পর্শকীয় বল $F = 2.5\text{ N}$ হলে তরলটির সান্দ্রতা গুণাঙ্ক $\eta$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 25)।</t>
+          <t>নিউটনীয় সান্দ্র বলের সূত্র: $F = \eta A \frac{v}{d} \implies \eta = \frac{F d}{A v} = \frac{2.5 \times (2\times 10^{-3})}{0.1 \times 0.5} = \frac{5.0\times 10^{-3}}{0.05} = 0.10\text{ Pa}\cdot\text{s} = 0.10\text{ N}\cdot\text{s/m}^2$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>সান্দ্রতা গুণাঙ্ক $\eta = 0.10\text{ Pa}\cdot\text{s}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4844,7 +4585,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক (সমস্যা 26)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4857,25 +4598,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক]
-$L = 1.0\text{ m}$ দৈর্ঘ্য এবং $r = 3\text{ cm}$ ব্যাসার্ধের একটি নিরেট ধাতব দণ্ডের এক প্রান্ত দৃঢ়ভাবে আটকে অপর প্রান্তে $\theta = 4^\circ$ মোচড় দিতে কত টর্কের প্রয়োজন হবে? (দৃঢ়তার গুণাঙ্ক $\eta = 4 \times 10^{10}\text{ N/m}^2$)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি নলের ভেতর পানির প্রবাহের ক্রান্তিক বেগ (Critical velocity) নির্ণয় কর। নলের ব্যাস $d = 2.0\text{ cm}$, পানির সান্দ্রতা $\eta = 1.0 	imes 10^{-3}\text{ Pa}\cdot\text{s}$ এবং রেনল্ডস সংখ্যা $R_e = 2000$ (ধারারেখ প্রবাহের সর্বোচ্চ সীমা)।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 26)।</t>
+          <t>রেনল্ডস সংখ্যা: $R_e = \frac{\rho v_c d}{\eta} \implies v_c = \frac{R_e \eta}{\rho d} = \frac{2000 \times 10^{-3}}{1000 \times 0.02} = \frac{2}{20} = 0.10\text{ m/s} = 10.0\text{ cm/s}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>ক্রান্তিক বেগ $v_c = 0.10\text{ m/s} = 10.0\text{ cm/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4895,38 +4636,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>তারের একক আয়তনে সঞ্চিত শক্তি (সমস্যা 27)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: তারের একক আয়তনে সঞ্চিত শক্তি]
-$Y = 2.0 \times 10^{11}\text{ N/m}^2$ বিশিষ্ট একটি তারে টান প্রয়োগ করে $0.4\%$ অনুদৈর্ঘ্য বিকৃতি ঘটানো হলো। তারটির প্রতি ঘনমিটার আয়তনে সঞ্চিত স্থিতিস্থাপক স্থিতিশক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+সান্দ্র তরলে পতনশীল একটি গোলকের প্রান্তীয় বেগ অর্জনের মুহূর্তে লব্ধি বলের মান কত এবং কেন ত্বরণ শূন্য হয় তা ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 27)।</t>
+          <t>পতনশীল গোলকের ওপর তিনটি বল কাজ করে: নিম্নমুখী ওজন $W = mg$, উর্ধ্বমুখী প্লবতা $F_B$ এবং উর্ধ্বমুখী সান্দ্র বাধা $F_v = 6\pi\eta r v$। বেগ বৃদ্ধির সাথে সাথে সান্দ্র বল বৃদ্ধি পেতে পেতে একপর্যায়ে $W = F_B + F_v$ হয়। তখন লব্ধি বল শূন্য হয় এবং নিউটনের ১ম সূত্রানুসারে ত্বরণ শূন্য হয়ে বস্তুটি ধ্রুব সমবেগে (প্রান্তিক বেগ) পড়তে থাকে।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>লব্ধি বল শূন্য ($F_{net} = 0$), ওজনের সমান সান্দ্র বল ও প্লবতা ক্রিয়াশীল</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4946,7 +4687,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ (সমস্যা 28)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4959,25 +4700,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ]
-একটি অনুভূমিক নলে পানি প্রবাহিত হচ্ছে। নলের যে অংশের প্রস্থচ্ছেদ $A_1 = 5\text{ cm}^2$, সেখানে বেগ $v_1 = 2\text{ m/s}$ এবং চাপ $P_1 = 1.5 \times 10^5\text{ Pa}$। অন্য প্রান্তে যেখানে $A_2 = 8\text{ cm}^2$, সেখানে পানির বেগ ও চাপ কত?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি সরু নলে পানির প্রবাহের জন্য পয়েসিলির সূত্রে চাপের নতিমাত্রা $\frac{dP}{dx} = 400\text{ Pa/m}$। নলের ব্যাসার্ধ $R = 2.0\text{ mm}$ এবং $\eta = 1.0 	imes 10^{-3}\text{ Pa}\cdot\text{s}$ হলে নলের অক্ষ বরাবর পানির সর্বোচ্চ বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 28)।</t>
+          <t>নলের অক্ষ বরাবর বেগ সর্বোচ্চ: $v(r) = \frac{1}{4\eta}\frac{dP}{dx}(R^2 - r^2)$। কেন্দ্রে $r = 0$: $v_{\max} = \frac{1}{4\eta}\frac{dP}{dx}R^2 = \frac{400 \times (2\times 10^{-3})^2}{4 \times 10^{-3}} = \frac{400 \times 4\times 10^{-6}}{4\times 10^{-3}} = 0.40\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>সর্বোচ্চ বেগ $v_{\max} = 0.40\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4997,38 +4738,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>টরেসেলির উপপাদ্য ও নির্গমন বেগ (সমস্যা 29)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: টরেসেলির উপপাদ্য ও নির্গমন বেগ]
-একটি পানির ট্যাংকের তলদেশ থেকে $h = 6\text{ m}$ নিচে একটি ক্ষুদ্র ছিদ্র রয়েছে। ছিদ্র দিয়ে পানি নির্গমনের বেগ ($v = \sqrt{2gh}$) এবং প্রতি সেকেন্ডে নির্গত পানির আয়তন কত? (ছিদ্রের ক্ষেত্রফল $A = 1\text{ cm}^2$)</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি গোলকের প্রান্তীয় বেগের ক্ষেত্রে সান্দ্র বলের দ্বারা প্রতি সেকেন্ডে উৎপন্ন তাপীয় ক্ষমতা প্রান্তীয় বেগের বর্গের সাথে কীভাবে সম্পর্কিত?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 29)।</t>
+          <t>প্রান্তিক বেগে সান্দ্র বলের বিরুদ্ধে কাজ তাপে পরিণত হয়: $P = F_v v_t = (6\pi\eta r v_t) v_t = 6\pi\eta r v_t^2$। যেহেতু $v_t \propto r^2$, সুতরাং ক্ষমতা $P \propto r(r^2)^2 = r^5$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>উৎপন্ন ক্ষমতা $P = 6\pi\eta r v_t^2 \propto v_t^2 \propto r^5$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5048,7 +4789,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>পয়সনের অনুপাত ও ব্যাস হ্রাস (সমস্যা 30)</t>
+          <t>সান্দ্রতা, স্টোকসের সূত্র ও প্রান্তিক বেগ (Viscosity, Stokes &amp; Fluid Flow)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5061,25 +4802,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: পয়সনের অনুপাত ও ব্যাস হ্রাস]
-একটি তারের ওপর টান বল প্রয়োগ করায় এর দৈর্ঘ্য বিকৃতি $0.1\%$ ঘটে। উপাদানটির পয়সনের অনুপাত $\sigma = 0.2$ হলে তারটির ব্যাস শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+একটি বড় তেলের ট্যাংকের তলায় একটি $2\text{ cm}^2$ ছিদ্র আছে। তেলের উচ্চতা $h = 5\text{ m}$ হলে ছিদ্র দিয়ে প্রতি সেকেন্ডে কত লিটার তেল নির্গত হবে? (টরিসেলির উপপাদ্য, $g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 30)।</t>
+          <t>নির্গমন বেগ $v = \sqrt{2gh} = \sqrt{2(9.8)(5)} = \sqrt{98} \approx 9.899\text{ m/s}$। প্রবাহের হার $Q = A v = (2\times 10^{-4}\text{ m}^2)(9.899\text{ m/s}) \approx 1.98\times 10^{-3}\text{ m}^3/\text{s} = 1.98\text{ L/s}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>প্রবাহের হার $Q = 1.98\\text{ লিটার/সেকেন্ড}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5099,43 +4840,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ (সমস্যা 31)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[সমস্যা 31: ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ]
-##GEO:cylinder[r=2,h=8][size:small]##
-$L = 2\text{ m}$ দীর্ঘ এবং $r = 4\text{ mm}$ ব্যাসার্ধবিশিষ্ট একটি ইস্পাত তারে $M = 25\text{ kg}$ ভর ঝুলালে তারটির দৈর্ঘ্য বৃদ্ধি কত হবে? ($Y = 2.0 \times 10^{11}\text{ N/m}^2, g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি অনুভূমিক পাইপের মধ্য দিয়ে পানি প্রবাহিত হচ্ছে। পাইপের প্রশস্ত অংশের ব্যাস $D_1 = 10\text{ cm}$ এবং সেখানে প্রবাহ বেগ $v_1 = 2\text{ m/s}$। সংকীর্ণ অংশের ব্যাস $D_2 = 5\text{ cm}$ হলে সংকীর্ণ অংশে পানির প্রবাহ বেগ এবং দুই অংশের মধ্যকার চাপের পার্থক্য কত? (পানির ঘনত্ব $1000\text{ kg/m}^3$)।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=2,h=8][size:small]##</t>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 31)।</t>
+          <t>ধারাবাহিকতার সমীকরণ: $A_1 v_1 = A_2 v_2 \implies v_2 = v_1\left(\frac{D_1}{D_2}\right)^2 = 2\left(\frac{10}{5}\right)^2 = 2(4) = 8.0\text{ m/s}$। বার্নোলির সমীকরণ: $P_1 + \frac{1}{2}\rho v_1^2 = P_2 + \frac{1}{2}\rho v_2^2 \implies P_1 - P_2 = \frac{1}{2}\rho(v_2^2 - v_1^2) = \frac{1}{2}(1000)(64 - 4) = 500(60) = 30000\text{ Pa} = 3.0\times 10^4\text{ Pa}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>সংকীর্ণ অংশে বেগ $v_2 = 8.0\text{ m/s}$, চাপের পার্থক্য $\Delta P = 3.0 \times 10^4\text{ Pa}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5155,12 +4891,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>স্টোকসের সূত্র ও প্রান্তিক বেগ (সমস্যা 32)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5168,30 +4904,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: স্টোকসের সূত্র ও প্রান্তিক বেগ]
-##GEO:sphere[r=4][size:small]##
-$\rho = 7800\text{ kg/m}^3$ ঘনত্বের একটি ক্ষুদ্র লোহার গোলক $\sigma = 900\text{ kg/m}^3$ ঘনত্ব এবং $\eta = 0.8\text{ Pa}\cdot\text{s}$ সান্দ্রতা বিশিষ্ট তেলে ছেড়ে দেওয়া হলো। গোলকের ব্যাসার্ধ $r = 3\text{ mm}$ হলে প্রান্তিক বেগ ($v_t$) কত?</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি ভেনচুরিমিটারে (Venturimeter) মূল নলের ব্যাস $8\text{ cm}$ এবং গ্রীবার (Throat) ব্যাস $4\text{ cm}$। নলের মধ্য দিয়ে প্রবাহিত পানির জন্য দুই অংশের ম্যানোমিটারের চাপের পার্থক্য $h = 20\text{ cm}$ পানির স্তম্ভ। পাইপ দিয়ে প্রতি সেকেন্ডে কত লিটার পানি প্রবাহিত হচ্ছে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 32)।</t>
+          <t>ভেনচুরির প্রবাহ সূত্র: $Q = A_1 A_2 \sqrt{\frac{2gh}{A_1^2 - A_2^2}} = A_2 \sqrt{\frac{2gh}{1 - (A_2/A_1)^2}}$। $A_2/A_1 = (4/8)^2 = 1/4 \implies (A_2/A_1)^2 = 1/16$। $A_2 = \frac{\pi}{4}(0.04^2) \approx 1.257\times 10^{-3}\text{ m}^2$। $\sqrt{\frac{2(9.8)(0.20)}{1 - 1/16}} = \sqrt{\frac{3.92}{15/16}} = \sqrt{4.181} \approx 2.045\text{ m/s}$। $Q = (1.257\times 10^{-3})(2.045) \approx 2.57\times 10^{-3}\text{ m}^3/\text{s} \approx 2.57\text{ L/s}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>প্রবাহের হার $Q = 2.65\text{ লিটার/সেকেন্ড}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5211,38 +4942,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান (সমস্যা 33)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান]
-$r = 0.4\text{ mm}$ ব্যাসার্ধের একটি কৈশিক নলকে পানিতে খাড়াভাবে ডুবালে পানি নলের ভেতর $h = 8\text{ cm}$ ওপরে ওঠে। পানির পৃষ্ঠটান $T$ নির্ণয় কর। (পানির ঘনত্ব $\rho = 1000\text{ kg/m}^3, g = 9.8\text{ m/s}^2$, স্পর্শ কোণ $\theta = 0^\circ$)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি বিমানের ডানার ওপর ও নিচের ক্ষেত্রফল $A = 25\text{ m}^2$। উড্ডয়নের সময় ডানার ওপরের পৃষ্ঠে বাতাসের বেগ $v_1 = 80\text{ m/s}$ এবং নিচের পৃষ্ঠে বাতাসের বেগ $v_2 = 65\text{ m/s}$। বাতাসের ঘনত্ব $\rho = 1.2\text{ kg/m}^3$ হলে ডানার ওপর প্রযুক্ত মোট লিফট বল (Dynamic lift) কত?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 33)।</t>
+          <t>বার্নোলির নীতি: $\Delta P = \frac{1}{2}\rho(v_1^2 - v_2^2) = \frac{1}{2}(1.2)(80^2 - 65^2) = 0.6(6400 - 4225) = 0.6(2175) = 1305\text{ N/m}^2$। মোট লিফট বল $F_{lift} = \Delta P \times A = 1305 \times 25 = 32625.0\text{ N} = 32.625\text{ kN}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>উর্ধমুখী লিফট বল $F_{lift} = 32625.0\text{ N} \approx 32.6\text{ kN}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5262,12 +4993,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>সাবান বুদবুদের অতিরিক্ত চাপ (সমস্যা 34)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5275,25 +5006,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: সাবান বুদবুদের অতিরিক্ত চাপ]
-বাতাসে $R = 5\text{ cm}$ ব্যাসার্ধের একটি সাবানের বুদবুদ তৈরি করা হলো। সাবান পানির পৃষ্ঠটান $T = 0.03\text{ N/m}$ হলে বুদবুদের ভেতরের অতিরিক্ত চাপ $\Delta P = \frac{4T}{R}$ কত প্যাস্কেল?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=3.5][size:small]##
+একটি পিটট নলের (Pitot tube) সাহায্যে আকাশে উড়ন্ত বিমানের বেগ পরিমাপ করা হচ্ছে। নলের ম্যানোমিটারে অ্যালকোহলের (আপেক্ষিক গুরুত্ব $0.80$) স্তরের পার্থক্য $10\text{ cm}$ পাওয়া গেল। বাতাসের ঘনত্ব $1.25\text{ kg/m}^3$ হলে বিমানের বেগ কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 34)।</t>
+          <t>চাপ পার্থক্য $\Delta P = \rho_m g h = (800)(9.8)(0.10) = 784\text{ Pa}$। পিটট নলের বেগ সমীকরণ: $v = \sqrt{\frac{2\Delta P}{\rho_{air}}} = \sqrt{\frac{2(784)}{1.25}} = \sqrt{\frac{1568}{1.25}} = \sqrt{1254.4} \approx 35.42\text{ m/s} \approx 127.5\text{ km/h}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>বিমানের দ্রুতি $v = 35.42\text{ m/s} \approx 127.5\text{ km/h}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5313,38 +5044,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>আয়তন গুণাঙ্ক ও সংনম্যতা (সমস্যা 35)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: আয়তন গুণাঙ্ক ও সংনম্যতা]
-একটি তরলের ওপর চাপ $\Delta P = 6 \times 10^6\text{ Pa}$ বৃদ্ধি করায় এর আয়তন $0.2\%$ হ্রাস পায়। তরলটির আয়তন গুণাঙ্ক ($K$) এবং সংনম্যতা ($k = 1/K$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি ছাদের পানির ট্যাংকের উচ্চতা ভূমি হতে $12\text{ m}$। গ্রাউন্ড ফ্লোরে থাকা নলের মুখের ব্যাস $1.0\text{ cm}$ হলে নলটি খুলে দিলে পানি কত বেগে বের হবে এবং প্রতি মিনিটে কত কেজি পানি নির্গত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 35)।</t>
+          <t>টরিসেলির বেগ $v = \sqrt{2gh} = \sqrt{2(9.8)(12)} = \sqrt{235.2} \approx 15.336\text{ m/s}$। প্রস্থচ্ছেদ $A = \frac{\pi}{4}(0.01^2) \approx 7.854\times 10^{-5}\text{ m}^2$। প্রতি সেকেন্ডে ভর $\frac{dm}{dt} = \rho A v = 1000(7.854\times 10^{-5})(15.336) \approx 1.2045\text{ kg/s}$। প্রতি মিনিটে নির্গমন $= 1.2045 \times 60 \approx 72.27\text{ kg/min}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>বেগ $v = 15.34\text{ m/s}$, নির্গমন হার $= 72.26\text{ kg/মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5364,12 +5095,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক (সমস্যা 36)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5377,25 +5108,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক]
-$L = 1.0\text{ m}$ দৈর্ঘ্য এবং $r = 1\text{ cm}$ ব্যাসার্ধের একটি নিরেট ধাতব দণ্ডের এক প্রান্ত দৃঢ়ভাবে আটকে অপর প্রান্তে $\theta = 4^\circ$ মোচড় দিতে কত টর্কের প্রয়োজন হবে? (দৃঢ়তার গুণাঙ্ক $\eta = 4 \times 10^{10}\text{ N/m}^2$)</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি অনুভূমিক নলে পানির প্রবাহের বেগ $v = 3\text{ m/s}$ এবং চাপ $P = 2.0 	imes 10^5\text{ Pa}$। পাইপটি এমন স্থানে পৌঁছাল যেখানে বেগ বৃদ্ধি পেয়ে $v' = 5\text{ m/s}$ হয়। ওই স্থানে পানির চাপ কত? (পানির ঘনত্ব $1000\text{ kg/m}^3$)।</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 36)।</t>
+          <t>বার্নোলির নীতি: $P + \frac{1}{2}\rho v^2 = P' + \frac{1}{2}\rho v'^2 \implies P' = P - \frac{1}{2}\rho(v'^2 - v^2) = 2.0\times 10^5 - 500(25 - 9) = 200000 - 500(16) = 200000 - 8000 = 192000\text{ Pa} = 1.92\times 10^5\text{ Pa}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>নতুন চাপ $P' = 1.92 \times 10^5\text{ Pa}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5415,38 +5146,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>তারের একক আয়তনে সঞ্চিত শক্তি (সমস্যা 37)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: তারের একক আয়তনে সঞ্চিত শক্তি]
-$Y = 2.0 \times 10^{11}\text{ N/m}^2$ বিশিষ্ট একটি তারে টান প্রয়োগ করে $0.2\%$ অনুদৈর্ঘ্য বিকৃতি ঘটানো হলো। তারটির প্রতি ঘনমিটার আয়তনে সঞ্চিত স্থিতিস্থাপক স্থিতিশক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=3][size:small]##
+একটি অ্যাটোমাইজার বা সুগন্ধি স্প্রেয়ারের নলের ব্যাস $1.5\text{ cm}$ থেকে সরু হয়ে অগ্রভাগে $0.3\text{ cm}$ হয়। অগ্রভাগে বাতাসের বেগ $40\text{ m/s}$ হলে নলের প্রশস্ত অংশে বাতাসের বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 37)।</t>
+          <t>ধারাবাহিকতার সমীকরণ: $A_1 v_1 = A_2 v_2 \implies v_1 = v_2\left(\frac{d_2}{d_1}\right)^2 = 40\left(\frac{0.3}{1.5}\right)^2 = 40\left(\frac{1}{5}\right)^2 = \frac{40}{25} = 1.60\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>প্রশস্ত অংশে বেগ $v_1 = 1.60\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5466,12 +5197,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ (সমস্যা 38)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5479,25 +5210,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ]
-একটি অনুভূমিক নলে পানি প্রবাহিত হচ্ছে। নলের যে অংশের প্রস্থচ্ছেদ $A_1 = 3\text{ cm}^2$, সেখানে বেগ $v_1 = 2\text{ m/s}$ এবং চাপ $P_1 = 1.5 \times 10^5\text{ Pa}$। অন্য প্রান্তে যেখানে $A_2 = 8\text{ cm}^2$, সেখানে পানির বেগ ও চাপ কত?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ম্যাগনেস প্রভাবের (Magnus effect) প্রয়োগ: স্পিন করা ফুটবল বাতাসে বক্রপথে বেঁকে যাওয়ার কারণ বার্নোলির উপপাদ্যের সাহায্যে ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 38)।</t>
+          <t>যখন কোনো বল ঘূর্ণনরত অবস্থায় বাতাসে এগিয়ে যায়, তখন বলের একপাশে তার পৃষ্ঠীয় ঘূর্ণনের দিক বাতাসের প্রবাহের অভিমুখে থাকে (ফলে মোট আপেক্ষিক বেগ বৃদ্ধি পায় এবং বার্নোলির নীতি অনুসারে চাপ হ্রাস পায়)। অপরপাশে ঘূর্ণন বাতাসের বিপরীতমুখী হওয়ায় বেগ হ্রাস পায় এবং চাপ বৃদ্ধি পায়। এই দুই পাশের চাপের পার্থক্যের কারণে বলের ওপর নিম্নচাপের দিকে একটি পার্শ্বীয় লব্ধি বল (ম্যাগনেস বল) সৃষ্টি হয় এবং বলটি বাঁকা পথে চলে।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>বলের একপাশে বাতাসের আপেক্ষিক বেগ বৃদ্ধি পাওয়ায় চাপ হ্রাস পায় এবং লব্ধি চাপ বলের দিকে বলটি বেঁকে যায়</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5517,38 +5248,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>টরেসেলির উপপাদ্য ও নির্গমন বেগ (সমস্যা 39)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: টরেসেলির উপপাদ্য ও নির্গমন বেগ]
-একটি পানির ট্যাংকের তলদেশ থেকে $h = 4\text{ m}$ নিচে একটি ক্ষুদ্র ছিদ্র রয়েছে। ছিদ্র দিয়ে পানি নির্গমনের বেগ ($v = \sqrt{2gh}$) এবং প্রতি সেকেন্ডে নির্গত পানির আয়তন কত? (ছিদ্রের ক্ষেত্রফল $A = 1\text{ cm}^2$)</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=5][size:small]##
+একটি সিলিন্ডারের দেয়ালে $H$ উচ্চতার তরল পূর্ণ আছে। দেয়ালের কত গভীরতায় একটি ক্ষুদ্র ছিদ্র করলে নির্গত পানির আনুভূমিক পাল্লা (Horizontal range on floor) সর্বোচ্চ হবে? সর্বোচ্চ পাল্লার মান কত?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 39)।</t>
+          <t>পৃষ্ঠ হতে $h$ গভীরতায় নির্গমন বেগ $v = \sqrt{2gh}$। মেঝে পর্যন্ত পতনের উচ্চতা $(H-h) = \frac{1}{2}g t^2 \implies t = \sqrt{\frac{2(H-h)}{g}}$। অনুভূমিক পাল্লা $R = v t = \sqrt{2gh}\sqrt{\frac{2(H-h)}{g}} = 2\sqrt{h(H-h)}$। সর্বোচ্চ পাল্লার জন্য $h(H-h)$ সর্বোচ্চ হতে হবে $\implies h = H/2$। তখন $R_{\max} = 2\sqrt{\frac{H}{2}\cdot\frac{H}{2}} = 2\left(\frac{H}{2}\right) = H$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>গভীরতা $h = H/2$, সর্বোচ্চ পাল্লা $R_{\max} = H$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5568,12 +5299,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>পয়সনের অনুপাত ও ব্যাস হ্রাস (সমস্যা 40)</t>
+          <t>বার্নোলির উপপাদ্য, ভেনচুরিমিটার ও প্রবাহী গতিবিদ্যা (Bernoulli &amp; Fluid Dynamics)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5581,25 +5312,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: পয়সনের অনুপাত ও ব্যাস হ্রাস]
-একটি তারের ওপর টান বল প্রয়োগ করায় এর দৈর্ঘ্য বিকৃতি $0.5\%$ ঘটে। উপাদানটির পয়সনের অনুপাত $\sigma = 0.2$ হলে তারটির ব্যাস শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+পানির মুক্ত তলের $10\text{ cm}$ নিচে অবস্থিত একটি ছিদ্রের ক্ষেত্রফল $1.0\text{ mm}^2$ হলে ছিদ্র দিয়ে প্রতি মিনিটে কত গ্রাম পানি নির্গত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 40)।</t>
+          <t>বেগ $v = \sqrt{2gh} = \sqrt{2(9.8)(0.10)} = \sqrt{1.96} = 1.40\text{ m/s}$। ক্ষেত্রফল $A = 10^{-6}\text{ m}^2$। প্রতি সেকেন্ডে পানির ভর $\frac{dm}{dt} = \rho A v = 1000(10^{-6})(1.40) = 1.40\times 10^{-3}\text{ kg/s} = 1.40\text{ g/s}$। প্রতি মিনিটে নির্গমন $= 1.40 \times 60 = 84.0\text{ g/min}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>নির্গমন $= 84.0\text{ g/মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5619,43 +5350,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ (সমস্যা 41)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[সমস্যা 41: ইয়ং-এর গুণাঙ্ক ও তারের প্রসারণ]
-##GEO:cylinder[r=2,h=8][size:small]##
-$L = 6\text{ m}$ দীর্ঘ এবং $r = 4\text{ mm}$ ব্যাসার্ধবিশিষ্ট একটি ইস্পাত তারে $M = 40\text{ kg}$ ভর ঝুলালে তারটির দৈর্ঘ্য বৃদ্ধি কত হবে? ($Y = 2.0 \times 10^{11}\text{ N/m}^2, g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি হাইড্রোলিক প্রেসের ছোট পিস্টনের ব্যাস $2\text{ cm}$ এবং বড় পিস্টনের ব্যাস $20\text{ cm}$। ছোট পিস্টনে $50\text{ N}$ বল প্রয়োগ করলে বড় পিস্টনে কত উর্ধ্বমুখী বল প্রযুক্ত হবে এবং ছোট পিস্টন $10\text{ cm}$ নিচে নামলে বড় পিস্টন কত সেন্টিমিটার উপরে উঠবে?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=2,h=8][size:small]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 41)।</t>
+          <t>প্যাসকেলের সূত্র: $\frac{F_2}{F_1} = \frac{A_2}{A_1} = \left(\frac{D_2}{D_1}\right)^2 = \left(\frac{20}{2}\right)^2 = 100 \implies F_2 = 100 \times 50 = 5000.0\text{ N}$। অসংকোচ্য তরলের আয়তন ধ্রুব: $A_1 h_1 = A_2 h_2 \implies h_2 = h_1 \frac{A_1}{A_2} = 10 \times \frac{1}{100} = 0.10\text{ cm} = 1.0\text{ mm}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>বড় পিস্টনে বল $F_2 = 5000.0\text{ N}$, উপরে উঠবে $h_2 = 0.10\text{ cm} = 1.0\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5675,12 +5401,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>স্টোকসের সূত্র ও প্রান্তিক বেগ (সমস্যা 42)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5688,30 +5414,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: স্টোকসের সূত্র ও প্রান্তিক বেগ]
-##GEO:sphere[r=4][size:small]##
-$\rho = 7800\text{ kg/m}^3$ ঘনত্বের একটি ক্ষুদ্র লোহার গোলক $\sigma = 900\text{ kg/m}^3$ ঘনত্ব এবং $\eta = 0.8\text{ Pa}\cdot\text{s}$ সান্দ্রতা বিশিষ্ট তেলে ছেড়ে দেওয়া হলো। গোলকের ব্যাসার্ধ $r = 1\text{ mm}$ হলে প্রান্তিক বেগ ($v_t$) কত?</t>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+একটি আবদ্ধ ট্যাংকে পানির উচ্চতা $h = 4\text{ m}$ এবং পানির উপরিভাগের ফাঁকা স্থানে আবদ্ধ বাতাসের গেজ চাপ $2.0 	imes 10^5\text{ Pa}$। ট্যাংকের তলদেশে থাকা একটি সরু ছিদ্র দিয়ে পানি নির্গমনের বেগ কত? ($g = 9.8\text{ ms}^{-2}, \rho = 1000\text{ kg/m}^3$)।</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 42)।</t>
+          <t>চাপযুক্ত ট্যাংকের জন্য টরিসেলির বর্ধিত রূপ: $v = \sqrt{2gh + \frac{2\Delta P}{\rho}} = \sqrt{2(9.8)(4) + \frac{2(2\times 10^5)}{1000}} = \sqrt{78.4 + 400} = \sqrt{478.4} \approx 21.87\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>নির্গমন বেগ $v = 21.87\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5731,38 +5452,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান (সমস্যা 43)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: কৈশিক নলে তরলের আরোহণ ও পৃষ্ঠটান]
-$r = 0.2\text{ mm}$ ব্যাসার্ধের একটি কৈশিক নলকে পানিতে খাড়াভাবে ডুবালে পানি নলের ভেতর $h = 8\text{ cm}$ ওপরে ওঠে। পানির পৃষ্ঠটান $T$ নির্ণয় কর। (পানির ঘনত্ব $\rho = 1000\text{ kg/m}^3, g = 9.8\text{ m/s}^2$, স্পর্শ কোণ $\theta = 0^\circ$)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি ধাতব তারের দৈর্ঘ্য বরাবর টান দিয়ে স্থিতিস্থাপক হিস্টেরেসিস লুপ (Elastic hysteresis loop) সম্পন্ন করা হলো। লুপের আবদ্ধ ক্ষেত্রফল $250\text{ J/m}^3$। তারটির উপাদানটির আয়তন $2 	imes 10^{-4}\text{ m}^3$ হলে প্রতিটি প্রসারণ-সংকোচন চক্রে তারটিতে উৎপন্ন তাপের পরিমাণ কত জুল?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 43)।</t>
+          <t>প্রতি চক্রে প্রতি একক আয়তনে যান্ত্রিক শক্তির অপচয় = হিস্টেরেসিস লুপের ক্ষেত্রফল $= 250\text{ J/m}^3$। মোট অপচয়কৃত শক্তি $W = (\text{লুপ ক্ষেত্রফল}) \times V = 250 \times (2\times 10^{-4}) = 0.050\text{ J}$। এই সম্পূর্ণ শক্তি তারে তাপে রূপান্তরিত হয়।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>উৎপন্ন তাপ $H = 0.050\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5782,12 +5503,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>সাবান বুদবুদের অতিরিক্ত চাপ (সমস্যা 44)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5795,25 +5516,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: সাবান বুদবুদের অতিরিক্ত চাপ]
-বাতাসে $R = 3\text{ cm}$ ব্যাসার্ধের একটি সাবানের বুদবুদ তৈরি করা হলো। সাবান পানির পৃষ্ঠটান $T = 0.03\text{ N/m}$ হলে বুদবুদের ভেতরের অতিরিক্ত চাপ $\Delta P = \frac{4T}{R}$ কত প্যাস্কেল?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি $L = 1.0\text{ m}$ দীর্ঘ এবং $r = 5.0\text{ mm}$ ব্যাসার্ধের তারের মোচড় দৃঢ়তা (Torsional rigidity) $C = \frac{\pi \eta r^4}{2L}$। দৃঢ়তা গুণাঙ্ক $\eta = 8.0 	imes 10^{10}\text{ N/m}^2$ হলে তারটির একপ্রান্ত স্থির রেখে অপরপ্রান্তে $30^\circ$ মোচড় দিতে সম্পাদিত কাজের পরিমাণ কত?</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 44)।</t>
+          <t>মোচড় ধ্রুবক $C = \frac{\pi(8.0\times 10^{10})(5\times 10^{-3})^4}{2(1.0)} = \frac{\pi(8.0\times 10^{10})(6.25\times 10^{-10})}{2} = 25\pi \approx 78.54\text{ N}\cdot\text{m/rad}$। কোণ $\theta = 30^\circ = \frac{\pi}{6}\text{ rad}$। কৃতকাজ $W = \frac{1}{2}C\theta^2 = \frac{1}{2}(78.54)\left(\frac{\pi}{6}\right)^2 = \frac{1}{2}(78.54)(0.274) \approx 10.76\text{ J}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>কৃতকাজ $W = 10.68\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5833,38 +5554,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>আয়তন গুণাঙ্ক ও সংনম্যতা (সমস্যা 45)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: আয়তন গুণাঙ্ক ও সংনম্যতা]
-একটি তরলের ওপর চাপ $\Delta P = 4 \times 10^6\text{ Pa}$ বৃদ্ধি করায় এর আয়তন $0.2\%$ হ্রাস পায়। তরলটির আয়তন গুণাঙ্ক ($K$) এবং সংনম্যতা ($k = 1/K$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+সমুদ্রের পানিতে শব্দের বেগ $v = 1500\text{ m/s}$ এবং পানির ঘনত্ব $\rho = 1025\text{ kg/m}^3$। সমুদ্রের পানির বাল্ক মডুলাস (আয়তন গুণাঙ্ক) কত প্যাসকেল?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 45)।</t>
+          <t>তরলে শব্দের বেগ $v = \sqrt{\frac{B}{\rho}} \implies B = \rho v^2 = 1025 \times (1500)^2 = 1025 \times 2.25\times 10^6 \approx 2.306\times 10^9\text{ Pa} \approx 2.31\times 10^9\text{ N/m}^2$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>বাল্ক মডুলাস $B = 2.31 \times 10^9\text{ Pa}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5884,12 +5605,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক (সমস্যা 46)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5897,25 +5618,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: দৃঢ়তার গুণাঙ্ক ও মোচড় টর্ক]
-$L = 1.0\text{ m}$ দৈর্ঘ্য এবং $r = 5\text{ cm}$ ব্যাসার্ধের একটি নিরেট ধাতব দণ্ডের এক প্রান্ত দৃঢ়ভাবে আটকে অপর প্রান্তে $\theta = 4^\circ$ মোচড় দিতে কত টর্কের প্রয়োজন হবে? (দৃঢ়তার গুণাঙ্ক $\eta = 4 \times 10^{10}\text{ N/m}^2$)</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি ধমনীর ব্যাস $4.0\text{ mm}$ এবং রক্তের সান্দ্রতা $\eta = 4.0 	imes 10^{-3}\text{ Pa}\cdot\text{s}$। রক্তের ঘনত্ব $1060\text{ kg/m}^3$ হলে ধমনীতে রক্ত প্রবাহ ঘূর্ণিযুক্ত (Turbulent) না হয়ে শান্ত ধারারেখ থাকার জন্য রক্তের সর্বোচ্চ বেগ কত হতে হবে? ($R_e = 2000$)।</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 46)।</t>
+          <t>রেনল্ডস সমীকরণ: $v_{\max} = \frac{R_e \eta}{\rho d} = \frac{2000 \times (4.0\times 10^{-3})}{1060 \times (4\times 10^{-3})} = \frac{8}{4.24} \approx 1.887\text{ m/s} \approx 1.89\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>সর্বোচ্চ বেগ $v_{\max} = 1.89\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5935,38 +5656,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>তারের একক আয়তনে সঞ্চিত শক্তি (সমস্যা 47)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: তারের একক আয়তনে সঞ্চিত শক্তি]
-$Y = 2.0 \times 10^{11}\text{ N/m}^2$ বিশিষ্ট একটি তারে টান প্রয়োগ করে $0.6\%$ অনুদৈর্ঘ্য বিকৃতি ঘটানো হলো। তারটির প্রতি ঘনমিটার আয়তনে সঞ্চিত স্থিতিস্থাপক স্থিতিশক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:cube[s=3][size:small]##
+পানির মুক্ত তলে একটি ভাসমান কাঠের টুকরার $75\%$ অংশ পানিতে নিমজ্জিত থাকে। কাঠের উপাদানের ঘনত্ব কত এবং টুকরাটিকে সম্পূর্ণ পানিতে নিমজ্জিত রাখতে এর ওপর কাঠের ওজনের কত শতাংশ অতিরিক্ত বল প্রয়োগ করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:cube[s=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 47)।</t>
+          <t>প্লবতার নিয়ম: $V_{sub} \rho_w g = V \rho_{wood} g \implies \rho_{wood} = \frac{V_{sub}}{V}\rho_w = 0.75 \times 1000 = 750.0\text{ kg/m}^3$। সম্পূর্ণ ডোবালে প্লবতা $F_B = V \rho_w g = \frac{4}{3} W$। অতিরিক্ত বল $F_{ext} = F_B - W = \frac{4}{3}W - W = \frac{1}{3}W \approx 33.33\%$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>ঘনত্ব $\rho = 750.0\text{ kg/m}^3$, অতিরিক্ত বল ওজনের $33.33\%$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5986,12 +5707,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ (সমস্যা 48)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -5999,25 +5720,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: বার্নোলির নীতি ও নলের প্রস্থচ্ছেদ]
-একটি অনুভূমিক নলে পানি প্রবাহিত হচ্ছে। নলের যে অংশের প্রস্থচ্ছেদ $A_1 = 1\text{ cm}^2$, সেখানে বেগ $v_1 = 2\text{ m/s}$ এবং চাপ $P_1 = 1.5 \times 10^5\text{ Pa}$। অন্য প্রান্তে যেখানে $A_2 = 8\text{ cm}^2$, সেখানে পানির বেগ ও চাপ কত?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+একটি কাচের তলের ওপর পানির স্পর্শ কোণ $0^\circ$ হলেও মোমের ওপর পানির স্পর্শ কোণ প্রায় $110^\circ$। মোমের গায়ে পানির ফোঁটা ছড়িয়ে না পড়ে গোলকাকারে থাকার কারণ সংশক্তি ও আসঞ্জন বলের ভিত্তিতে গাণিতিকভাবে ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 48)।</t>
+          <t>ইয়ং-ডুপ্রে সমীকরণ: $\cos\theta = \frac{T_{sa} - T_{sl}}{T_{la}}$। যখন তরল-কঠিন আসঞ্জন বল ($F_a$) তরল অণুগুলোর পারস্পরিক সংশক্তি বল ($F_c$) অপেক্ষা দুর্বল হয় ($F_a &lt; F_c/\sqrt{2}$), তখন স্পর্শ কোণ স্থূলকোণ ($\theta &gt; 90^\circ$) হয় এবং তরল পৃষ্ঠপৃষ্ঠকে না ভিজিয়ে মুক্ত তল সঙ্কুচিত করে গোলকাকার ধারণ করে।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>আসঞ্জন বল অপেক্ষা পানির সংশক্তি বল বেশি হওয়ায় স্পর্শ কোণ স্থূলকোণ হয় এবং পানি মোমকে ভেজায় না</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6037,38 +5758,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>টরেসেলির উপপাদ্য ও নির্গমন বেগ (সমস্যা 49)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: টরেসেলির উপপাদ্য ও নির্গমন বেগ]
-একটি পানির ট্যাংকের তলদেশ থেকে $h = 2\text{ m}$ নিচে একটি ক্ষুদ্র ছিদ্র রয়েছে। ছিদ্র দিয়ে পানি নির্গমনের বেগ ($v = \sqrt{2gh}$) এবং প্রতি সেকেন্ডে নির্গত পানির আয়তন কত? (ছিদ্রের ক্ষেত্রফল $A = 1\text{ cm}^2$)</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:cube[s=3.5][size:small]##
+একটি $10\text{ cm}$ বাহুবিশিষ্ট সমসত্ত্ব তামার ঘনকের ওপর চারদিক থেকে সমভাবে $1.0 	imes 10^7\text{ N/m}^2$ জলীয় চাপ প্রয়োগ করা হলো। ঘনকটির আয়তন কত হ্রাস পাবে? (তামার বাল্ক মডুলাস $B = 1.3 	imes 10^{11}\text{ N/m}^2$)।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:cube[s=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 49)।</t>
+          <t>ঘনকের আদি আয়তন $V = a^3 = (0.10)^3 = 10^{-3}\text{ m}^3$। বাল্ক মডুলাস $B = \frac{\Delta P}{\Delta V / V} \implies \frac{\Delta V}{V} = \frac{\Delta P}{B} = \frac{1.0\times 10^7}{1.3\times 10^{11}} \approx 7.692\times 10^{-5}$। আয়তন হ্রাস $\Delta V = V \times 7.692\times 10^{-5} = 10^{-3} \times 7.692\times 10^{-5} = 7.692\times 10^{-8}\text{ m}^3 = 0.0769\text{ cm}^3$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>আয়তন হ্রাস $\Delta V = 7.69 \times 10^{-8}\text{ m}^3 = 0.077\text{ cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6088,12 +5809,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>পয়সনের অনুপাত ও ব্যাস হ্রাস (সমস্যা 50)</t>
+          <t>সান্দ্রতা, মোচড় দৃঢ়তা ও তরল ফোঁটার শক্তি রূপান্তর (Fluid Dynamics &amp; Torsion)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6101,25 +5822,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: পয়সনের অনুপাত ও ব্যাস হ্রাস]
-একটি তারের ওপর টান বল প্রয়োগ করায় এর দৈর্ঘ্য বিকৃতি $0.3\%$ ঘটে। উপাদানটির পয়সনের অনুপাত $\sigma = 0.2$ হলে তারটির ব্যাস শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+সমান ব্যাসার্ধ $r$ বিশিষ্ট $N$ টি ছোট তরল ফোঁটা একত্রিত হয়ে একটি একক বড় ফোঁটায় রূপান্তরিত হলে এর ফলে তরলের তাপমাত্রা বৃদ্ধি $\Delta T$-এর সমীকরণ প্রতিপাদন কর (তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং আপেক্ষিক তাপ $s$)।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>পদার্থের স্থিতিস্থাপকতা, পৃষ্ঠটান, সান্দ্রতা ও প্রবাহী গতিবিদ্যার মূল সূত্রানুসারে সমাধান (সমস্যা 50)।</t>
+          <t>আদি ক্ষেত্রফল $A_1 = N(4\pi r^2)$, শেষ ক্ষেত্রফল $A_2 = 4\pi R^2$ যেখানে $R = N^{1/3}r$। ক্ষেত্রফল হ্রাস $\Delta A = 4\pi(N r^2 - R^2) = 4\pi N r^3\left(\frac{1}{r} - \frac{1}{R}\right)$। মোট মুক্ত শক্তি $Q = T \Delta A$। এই তাপ মোট ভর $M = \rho \frac{4}{3}\pi R^3 = \rho N \frac{4}{3}\pi r^3$-কে উত্তপ্ত করে: $M s \Delta T = T \Delta A \implies \Delta T = \frac{T \Delta A}{M s} = \frac{T \cdot 4\pi N r^3(1/r - 1/R)}{\rho N \frac{4}{3}\pi r^3 s} = \frac{3T}{\rho s}\left(\frac{1}{r} - \frac{1}{R}\right)$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>গাঠনিক ধর্ম সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>$\Delta T = \frac{3T}{\rho s}\left(\frac{1}{r} - \frac{1}{R}\right)$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
